--- a/AAII_Financials/Quarterly/STEP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STEP_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
   <si>
     <t>STEP</t>
   </si>
@@ -656,302 +656,314 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3">
         <v>192800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>178600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>173100</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K8" s="3">
         <v>366500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>412300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>284200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>311000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>360400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>249500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>243600</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T8" s="3">
+      <c r="T8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U8" s="3">
         <v>131900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>99600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>44700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>11700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>13600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>41700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>89800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>102400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>101000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>110900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>144600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>83900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>83300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>40100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>40200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>24500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="3">
         <v>191100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>169500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>160300</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K10" s="3">
         <v>276700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>309900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>183200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>200100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>215800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>165600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>160300</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T10" s="3">
+      <c r="T10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U10" s="3">
         <v>91700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>75100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>39400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>60200</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -975,8 +987,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1040,8 +1053,11 @@
       <c r="W12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1105,8 +1121,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1116,26 +1135,26 @@
       <c r="E14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
         <v>-2700</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1170,8 +1189,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1182,7 +1204,7 @@
         <v>10700</v>
       </c>
       <c r="F15" s="3">
-        <v>10900</v>
+        <v>10700</v>
       </c>
       <c r="G15" s="3">
         <v>10900</v>
@@ -1194,19 +1216,19 @@
         <v>10900</v>
       </c>
       <c r="J15" s="3">
+        <v>10900</v>
+      </c>
+      <c r="K15" s="3">
         <v>11100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>11000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>600</v>
-      </c>
-      <c r="N15" s="3">
-        <v>800</v>
       </c>
       <c r="O15" s="3">
         <v>800</v>
@@ -1218,25 +1240,28 @@
         <v>800</v>
       </c>
       <c r="R15" s="3">
+        <v>800</v>
+      </c>
+      <c r="S15" s="3">
         <v>12700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>12200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1257,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E17" s="3">
         <v>130300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>121200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>100200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>-104200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>-68400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>273300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>292700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>173400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>173700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>205100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>136400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>133100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>-15100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>91700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>51600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>84300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>67000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>41200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>51600</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="3">
         <v>62500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>57400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>72900</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K18" s="3">
         <v>93200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>119600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>110800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>137300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>155300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>113100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>110500</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U18" s="3">
         <v>47600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>32600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>17800</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1412,118 +1444,122 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3">
         <v>6600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3700</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J20" s="3">
-        <v>23100</v>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K20" s="3">
         <v>23100</v>
       </c>
       <c r="L20" s="3">
+        <v>23100</v>
+      </c>
+      <c r="M20" s="3">
         <v>3000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>7600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>4000</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U20" s="3">
         <v>2400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="3">
         <v>81100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>72000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>81300</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K21" s="3">
         <v>128000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>154300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>116300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>142100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>164200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>118400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>115900</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1533,50 +1569,53 @@
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V21" s="3">
         <v>36000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X21" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E22" s="3">
         <v>2100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>600</v>
-      </c>
-      <c r="J22" s="3">
-        <v>500</v>
       </c>
       <c r="K22" s="3">
         <v>500</v>
       </c>
       <c r="L22" s="3">
+        <v>500</v>
+      </c>
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
@@ -1584,22 +1623,22 @@
         <v>0</v>
       </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>5300</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>4100</v>
       </c>
       <c r="R22" s="3">
         <v>4100</v>
       </c>
       <c r="S22" s="3">
+        <v>4100</v>
+      </c>
+      <c r="T22" s="3">
         <v>2400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2600</v>
-      </c>
-      <c r="U22" s="3">
-        <v>2700</v>
       </c>
       <c r="V22" s="3">
         <v>2700</v>
@@ -1607,138 +1646,147 @@
       <c r="W22" s="3">
         <v>2700</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-24100</v>
+      </c>
+      <c r="E23" s="3">
         <v>67000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>58000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>67500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-14300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-74500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-20200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>115800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>142100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>113700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>140900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>162900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>116900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>109300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-51200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>51500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>18200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>47400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>31600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E24" s="3">
         <v>7700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>10700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-7400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>12200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>15800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-14100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>14400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>11700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1802,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="E26" s="3">
         <v>59300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>49400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>56800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-13600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-67100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-21500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>103600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>126300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>127900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>126500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>151200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>107400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>108400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-52400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>50200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>17200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>46400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>31000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>15500</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="E27" s="3">
         <v>26200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>21300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>28800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-6900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-29200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-11000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>41800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>48300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>62100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>41700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>37800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>25600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-800</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
       <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
         <v>-84900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>12100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>44400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>28500</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
       <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1997,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2062,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2127,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2192,138 +2258,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="3">
         <v>-6600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3700</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J32" s="3">
-        <v>-23100</v>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K32" s="3">
         <v>-23100</v>
       </c>
       <c r="L32" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="M32" s="3">
         <v>-3000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-7600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U32" s="3">
         <v>-2400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="E33" s="3">
         <v>26200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>21300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>28800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-6900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-29200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-11000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>41800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>48300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>62100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>41700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>37800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>25600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-800</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
       <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
         <v>-84900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>12100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>44400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>28500</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
       <c r="W33" s="3">
+        <v>0</v>
+      </c>
+      <c r="X33" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2387,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="E35" s="3">
         <v>26200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>21300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>28800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-6900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-29200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-11000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>41800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>48300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>62100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>41700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>37800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>25600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-800</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
       <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
         <v>-84900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>12100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>44400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>28500</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
       <c r="W35" s="3">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2547,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2572,62 +2657,63 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>173600</v>
+      </c>
+      <c r="E41" s="3">
         <v>176100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>127200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>128600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>140100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>143600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>106400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>116400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>135900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>175000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>218600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>179900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>185000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>156900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>90700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>89900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>116100</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2637,8 +2723,11 @@
       <c r="W41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2702,62 +2791,65 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1958400</v>
+      </c>
+      <c r="E43" s="3">
         <v>2128500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2131800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2096600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2093800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2228300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2583900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2868600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2702700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2469100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1121500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>936100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>669900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>518900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>369300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>495600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>426500</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2767,8 +2859,11 @@
       <c r="W43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2832,8 +2927,11 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2897,8 +2995,11 @@
       <c r="W45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2962,62 +3063,65 @@
       <c r="W46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>236600</v>
+      </c>
+      <c r="E47" s="3">
         <v>198200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>161300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>145800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>123400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>107000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>108100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>107000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>98800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>90300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>82900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>74400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>63400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>57900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>50400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>53400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>49600</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>4</v>
       </c>
@@ -3027,44 +3131,47 @@
       <c r="W47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>97400</v>
+      </c>
+      <c r="E48" s="3">
         <v>99800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>100500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>101100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>104800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>62800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>72100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>61100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>63300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>65500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>64700</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3080,8 +3187,8 @@
       <c r="S48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
+      <c r="T48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
@@ -3092,62 +3199,65 @@
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>895800</v>
+      </c>
+      <c r="E49" s="3">
         <v>913900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>924500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>935200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>946100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>956900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>967800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>978700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>992400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1003100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>12300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>13100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>14000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>14800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>15600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>16600</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3157,8 +3267,11 @@
       <c r="W49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3222,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3287,62 +3403,65 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>46100</v>
+      </c>
+      <c r="E52" s="3">
         <v>37500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>39600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>45300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>50200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>40400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>32500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>28900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>20000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>98500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>93400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>39600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>47200</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R52" s="3">
+      <c r="R52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S52" s="3">
         <v>700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>600</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3352,8 +3471,11 @@
       <c r="W52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3417,62 +3539,65 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3468200</v>
+      </c>
+      <c r="E54" s="3">
         <v>3608400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3530800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3497400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3503100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3575600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3906200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4188100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4036600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3831500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1622800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1320800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>994800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>817700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>549400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>680800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>631500</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3482,8 +3607,11 @@
       <c r="W54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3507,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3532,62 +3661,63 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>78300</v>
+      </c>
+      <c r="E57" s="3">
         <v>66400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>66300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>67800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>64700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>63600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>55400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>61500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>41500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>48900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>24800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>33800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>28400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>29300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>25400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>36000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>40900</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3597,8 +3727,11 @@
       <c r="W57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3662,62 +3795,65 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1574300</v>
+      </c>
+      <c r="E59" s="3">
         <v>1687600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1670500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1655800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1725400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1787000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2023600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2220400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2095800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1917900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>815600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>613400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>418700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>350400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>213000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>264500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>238900</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>4</v>
       </c>
@@ -3727,8 +3863,11 @@
       <c r="W59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3792,41 +3931,44 @@
       <c r="W60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>123700</v>
+      </c>
+      <c r="E61" s="3">
         <v>123600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>98500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>98400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>83200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>63100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>63000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>62900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>62800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>112600</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3837,17 +3979,17 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>143000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>143100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>143300</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -3857,8 +3999,11 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3898,21 +4043,21 @@
       <c r="O62" s="3">
         <v>0</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>4</v>
+      <c r="P62" s="3">
+        <v>0</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R62" s="3">
+      <c r="R62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S62" s="3">
         <v>200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>400</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3922,8 +4067,11 @@
       <c r="W62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3987,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4052,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4117,62 +4271,65 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2706300</v>
+      </c>
+      <c r="E66" s="3">
         <v>2813700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2764800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2725800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2751400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2814400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3106400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3370500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3260900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3147900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1317800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1071400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>848600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>698200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>414200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>464600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>444900</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4182,8 +4339,11 @@
       <c r="W66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4207,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4272,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4337,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4402,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4467,53 +4637,56 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>131300</v>
+      </c>
+      <c r="E72" s="3">
         <v>165200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>152600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>160400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>144500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>164000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>205900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>229600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>197200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>158100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>99100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>60400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>24800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-800</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4532,8 +4705,11 @@
       <c r="W72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4597,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4662,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4727,62 +4909,65 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>761800</v>
+      </c>
+      <c r="E76" s="3">
         <v>794700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>766000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>771600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>751700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>761200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>799800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>817600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>775700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>683600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>304900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>249400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>146200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>119600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>135200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>216200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>186600</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>4</v>
       </c>
@@ -4792,8 +4977,11 @@
       <c r="W76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4857,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="E81" s="3">
         <v>26200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>21300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>28800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-6900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-29200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-11000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>41800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>48300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>62100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>41700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>37800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>25600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-800</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
       <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
         <v>-84900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>12100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>44400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>28500</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
       <c r="W81" s="3">
+        <v>0</v>
+      </c>
+      <c r="X81" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5017,46 +5214,47 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>12000</v>
+        <v>12200</v>
       </c>
       <c r="E83" s="3">
         <v>12000</v>
       </c>
       <c r="F83" s="3">
-        <v>12100</v>
+        <v>12000</v>
       </c>
       <c r="G83" s="3">
         <v>12100</v>
       </c>
       <c r="H83" s="3">
+        <v>12100</v>
+      </c>
+      <c r="I83" s="3">
         <v>11700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>11500</v>
-      </c>
-      <c r="J83" s="3">
-        <v>11700</v>
       </c>
       <c r="K83" s="3">
         <v>11700</v>
       </c>
       <c r="L83" s="3">
+        <v>11700</v>
+      </c>
+      <c r="M83" s="3">
         <v>2400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1300</v>
-      </c>
-      <c r="O83" s="3">
-        <v>1400</v>
       </c>
       <c r="P83" s="3">
         <v>1400</v>
@@ -5065,25 +5263,28 @@
         <v>1400</v>
       </c>
       <c r="R83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="S83" s="3">
         <v>1600</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V83" s="3">
         <v>1700</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5147,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5212,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5277,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5342,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5407,73 +5620,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E89" s="3">
         <v>71100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>57600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>88200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>57500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>32300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>46500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>59800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>75700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>29000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>37400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>53900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>28900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1900</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V89" s="3">
         <v>26400</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5497,73 +5716,77 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1200</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-300</v>
       </c>
       <c r="O91" s="3">
         <v>-300</v>
       </c>
       <c r="P91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-700</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U91" s="3">
+      <c r="U91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5627,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5692,73 +5918,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-12900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-14500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-9700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-184300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2200</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V94" s="3">
         <v>1300</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5782,41 +6014,42 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="E96" s="3">
         <v>-13300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-28300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-12600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-12900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-12300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-12200</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-9100</v>
       </c>
       <c r="K96" s="3">
         <v>-9100</v>
       </c>
       <c r="L96" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="M96" s="3">
         <v>-5600</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -5847,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5912,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5977,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6042,199 +6284,211 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-9500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-44000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-42100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-60700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-43400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-74200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>77600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-30500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-32800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>19400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-26600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-21800</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V100" s="3">
         <v>-10500</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1300</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-100</v>
       </c>
       <c r="P101" s="3">
         <v>-100</v>
       </c>
       <c r="Q101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-200</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3" t="s">
-        <v>4</v>
+      <c r="U101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
       </c>
       <c r="W101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E102" s="3">
         <v>48900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>37200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-10100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-19500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-39100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-46600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>38700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>29200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>69100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-26200</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V102" s="3">
         <v>17200</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/STEP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STEP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
   <si>
     <t>STEP</t>
   </si>
@@ -656,314 +656,327 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="D8" s="3">
+        <v>357900</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3">
         <v>192800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>178600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>173100</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L8" s="3">
         <v>366500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>412300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>284200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>311000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>360400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>249500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>243600</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U8" s="3">
+      <c r="U8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V8" s="3">
         <v>131900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>99600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>44700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E9" s="3">
         <v>15400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>11700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>13600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>41700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>89800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>102400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>101000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>110900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>144600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>83900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>83300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>40100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>40200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>24500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="D10" s="3">
+        <v>346500</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="3">
         <v>191100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>169500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>160300</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L10" s="3">
         <v>276700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>309900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>183200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>200100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>215800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>165600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>160300</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V10" s="3">
         <v>91700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>75100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>39400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>60200</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,8 +1001,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1056,8 +1070,11 @@
       <c r="X12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,13 +1141,16 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>-100</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>4</v>
@@ -1138,26 +1158,26 @@
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
         <v>-2700</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1192,13 +1212,16 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>10700</v>
+        <v>10400</v>
       </c>
       <c r="E15" s="3">
         <v>10700</v>
@@ -1207,7 +1230,7 @@
         <v>10700</v>
       </c>
       <c r="G15" s="3">
-        <v>10900</v>
+        <v>10700</v>
       </c>
       <c r="H15" s="3">
         <v>10900</v>
@@ -1219,19 +1242,19 @@
         <v>10900</v>
       </c>
       <c r="K15" s="3">
+        <v>10900</v>
+      </c>
+      <c r="L15" s="3">
         <v>11100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>11000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>600</v>
-      </c>
-      <c r="O15" s="3">
-        <v>800</v>
       </c>
       <c r="P15" s="3">
         <v>800</v>
@@ -1243,25 +1266,28 @@
         <v>800</v>
       </c>
       <c r="S15" s="3">
+        <v>800</v>
+      </c>
+      <c r="T15" s="3">
         <v>12700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>12200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1309,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>269200</v>
+      </c>
+      <c r="E17" s="3">
         <v>19200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>130300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>121200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>100200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>-104200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>-68400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>273300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>292700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>173400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>173700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>205100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>136400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>133100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>-15100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>91700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>51600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>84300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>67000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>41200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>51600</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" s="3">
+      <c r="D18" s="3">
+        <v>88700</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="3">
         <v>62500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>57400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>72900</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="3">
         <v>93200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>119600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>110800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>137300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>155300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>113100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>110500</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V18" s="3">
         <v>47600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>32600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>17800</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,124 +1478,128 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3">
         <v>6600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3700</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="3">
-        <v>23100</v>
+      <c r="K20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L20" s="3">
         <v>23100</v>
       </c>
       <c r="M20" s="3">
+        <v>23100</v>
+      </c>
+      <c r="N20" s="3">
         <v>3000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>7600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>4000</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V20" s="3">
         <v>2400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="3">
+      <c r="D21" s="3">
+        <v>108600</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="3">
         <v>81100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>72000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>81300</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L21" s="3">
         <v>128000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>154300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>116300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>142100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>164200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>118400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>115900</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1572,17 +1609,20 @@
       <c r="U21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W21" s="3">
         <v>36000</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y21" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1590,35 +1630,35 @@
         <v>2600</v>
       </c>
       <c r="E22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F22" s="3">
         <v>2100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>600</v>
-      </c>
-      <c r="K22" s="3">
-        <v>500</v>
       </c>
       <c r="L22" s="3">
         <v>500</v>
       </c>
       <c r="M22" s="3">
+        <v>500</v>
+      </c>
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
@@ -1626,22 +1666,22 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>5300</v>
-      </c>
-      <c r="R22" s="3">
-        <v>4100</v>
       </c>
       <c r="S22" s="3">
         <v>4100</v>
       </c>
       <c r="T22" s="3">
+        <v>4100</v>
+      </c>
+      <c r="U22" s="3">
         <v>2400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>2600</v>
-      </c>
-      <c r="V22" s="3">
-        <v>2700</v>
       </c>
       <c r="W22" s="3">
         <v>2700</v>
@@ -1649,144 +1689,153 @@
       <c r="X22" s="3">
         <v>2700</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>94500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-24100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>67000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>58000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>67500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-14300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-74500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-20200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>115800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>142100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>113700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>140900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>162900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>116900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>109300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-51200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>51500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>18200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>47400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>31600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>10700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-7400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>12200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>15800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-14100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>14400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>11700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>9500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>82500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-23400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>59300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>49400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>56800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-13600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-67100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-21500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>103600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>126300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>127900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>126500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>151200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>107400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>108400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-52400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>50200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>17200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>46400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>31000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>15500</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-20200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>26200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>21300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>28800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-29200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-11000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>41800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>48300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>62100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>41700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>37800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>25600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-800</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
       <c r="S27" s="3">
+        <v>0</v>
+      </c>
+      <c r="T27" s="3">
         <v>-84900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>12100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>44400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>28500</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
       <c r="X27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2186,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,144 +2328,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3">
         <v>-6600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3700</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K32" s="3">
-        <v>-23100</v>
+      <c r="K32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L32" s="3">
         <v>-23100</v>
       </c>
       <c r="M32" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="N32" s="3">
         <v>-3000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-7600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-4000</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V32" s="3">
         <v>-2400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-20200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>26200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>21300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>28800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-29200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-11000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>41800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>48300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>62100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>41700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>37800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>25600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-800</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
       <c r="S33" s="3">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3">
         <v>-84900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>12100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>44400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>28500</v>
       </c>
-      <c r="W33" s="3">
-        <v>0</v>
-      </c>
       <c r="X33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-20200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>26200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>21300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>28800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-29200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-11000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>41800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>48300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>62100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>41700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>37800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>25600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-800</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
       <c r="S35" s="3">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3">
         <v>-84900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>12100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>44400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>28500</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
-      </c>
       <c r="X35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,65 +2744,66 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>181600</v>
+      </c>
+      <c r="E41" s="3">
         <v>173600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>176100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>127200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>128600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>140100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>143600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>106400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>116400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>135900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>175000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>218600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>179900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>185000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>156900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>90700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>89900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>116100</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2726,8 +2813,11 @@
       <c r="X41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2794,65 +2884,68 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2109500</v>
+      </c>
+      <c r="E43" s="3">
         <v>1958400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2128500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2131800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2096600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2093800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2228300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2583900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2868600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2702700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2469100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1121500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>936100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>669900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>518900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>369300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>495600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>426500</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2862,8 +2955,11 @@
       <c r="X43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2930,8 +3026,11 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2998,8 +3097,11 @@
       <c r="X45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3066,65 +3168,68 @@
       <c r="X46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>266900</v>
+      </c>
+      <c r="E47" s="3">
         <v>236600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>198200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>161300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>145800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>123400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>107000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>108100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>107000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>98800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>90300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>82900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>74400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>63400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>57900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>50400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>53400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>49600</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>4</v>
       </c>
@@ -3134,47 +3239,50 @@
       <c r="X47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>97800</v>
+      </c>
+      <c r="E48" s="3">
         <v>97400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>99800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>100500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>101100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>104800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>62800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>72100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>61100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>63300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>65500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>64700</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3190,8 +3298,8 @@
       <c r="T48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
@@ -3202,65 +3310,68 @@
       <c r="X48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>885400</v>
+      </c>
+      <c r="E49" s="3">
         <v>895800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>913900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>924500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>935200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>946100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>956900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>967800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>978700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>992400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1003100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>11700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>12300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>13100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>14000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>14800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>15600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>16600</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3270,8 +3381,11 @@
       <c r="X49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,65 +3523,68 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>185200</v>
+      </c>
+      <c r="E52" s="3">
         <v>46100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>37500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>39600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>45300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>50200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>40400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>32500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>28900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>20000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>98500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>93400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>39600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>47200</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S52" s="3">
+      <c r="S52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T52" s="3">
         <v>700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>600</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3474,8 +3594,11 @@
       <c r="X52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,65 +3665,68 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3788800</v>
+      </c>
+      <c r="E54" s="3">
         <v>3468200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3608400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3530800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3497400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3503100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3575600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3906200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4188100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4036600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3831500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1622800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1320800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>994800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>817700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>549400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>680800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>631500</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3610,8 +3736,11 @@
       <c r="X54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,65 +3792,66 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>96400</v>
+      </c>
+      <c r="E57" s="3">
         <v>78300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>66400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>66300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>67800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>64700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>63600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>55400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>61500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>41500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>48900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>24800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>33800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>28400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>29300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>25400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>36000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>40900</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3730,8 +3861,11 @@
       <c r="X57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3798,65 +3932,68 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1637800</v>
+      </c>
+      <c r="E59" s="3">
         <v>1574300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1687600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1670500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1655800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1725400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1787000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2023600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2220400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2095800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1917900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>815600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>613400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>418700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>350400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>213000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>264500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>238900</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>4</v>
       </c>
@@ -3866,8 +4003,11 @@
       <c r="X59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3934,44 +4074,47 @@
       <c r="X60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>148800</v>
+      </c>
+      <c r="E61" s="3">
         <v>123700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>123600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>98500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>98400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>83200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>63100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>63000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>62900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>62800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>112600</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3982,17 +4125,17 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>143000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>143100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>143300</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4002,8 +4145,11 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4046,21 +4192,21 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>4</v>
+      <c r="Q62" s="3">
+        <v>0</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S62" s="3">
+      <c r="S62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T62" s="3">
         <v>200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>400</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4070,8 +4216,11 @@
       <c r="X62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,65 +4429,68 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3464300</v>
+      </c>
+      <c r="E66" s="3">
         <v>2706300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2813700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2764800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2725800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2751400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2814400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3106400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3370500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3260900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3147900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1317800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1071400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>848600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>698200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>414200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>464600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>444900</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4342,8 +4500,11 @@
       <c r="X66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4572,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,56 +4811,59 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E72" s="3">
         <v>131300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>165200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>152600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>160400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>144500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>164000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>205900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>229600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>197200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>158100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>99100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>60400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>24800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-800</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4708,8 +4882,11 @@
       <c r="X72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,65 +5095,68 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>324500</v>
+      </c>
+      <c r="E76" s="3">
         <v>761800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>794700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>766000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>771600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>751700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>761200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>799800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>817600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>775700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>683600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>304900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>249400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>146200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>119600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>135200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>216200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>186600</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>4</v>
       </c>
@@ -4980,8 +5166,11 @@
       <c r="X76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-20200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>26200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>21300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>28800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-29200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-11000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>41800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>48300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>62100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>41700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>37800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>25600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-800</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
       <c r="S81" s="3">
+        <v>0</v>
+      </c>
+      <c r="T81" s="3">
         <v>-84900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>12100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>44400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>28500</v>
       </c>
-      <c r="W81" s="3">
-        <v>0</v>
-      </c>
       <c r="X81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,49 +5413,50 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E83" s="3">
         <v>12200</v>
-      </c>
-      <c r="E83" s="3">
-        <v>12000</v>
       </c>
       <c r="F83" s="3">
         <v>12000</v>
       </c>
       <c r="G83" s="3">
-        <v>12100</v>
+        <v>12000</v>
       </c>
       <c r="H83" s="3">
         <v>12100</v>
       </c>
       <c r="I83" s="3">
+        <v>12100</v>
+      </c>
+      <c r="J83" s="3">
         <v>11700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>11500</v>
-      </c>
-      <c r="K83" s="3">
-        <v>11700</v>
       </c>
       <c r="L83" s="3">
         <v>11700</v>
       </c>
       <c r="M83" s="3">
+        <v>11700</v>
+      </c>
+      <c r="N83" s="3">
         <v>2400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1300</v>
-      </c>
-      <c r="P83" s="3">
-        <v>1400</v>
       </c>
       <c r="Q83" s="3">
         <v>1400</v>
@@ -5266,25 +5465,28 @@
         <v>1400</v>
       </c>
       <c r="S83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="T83" s="3">
         <v>1600</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V83" s="3">
+      <c r="V83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W83" s="3">
         <v>1700</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,76 +5837,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E89" s="3">
         <v>25200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>71100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>57600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>88200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>57500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>32300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>46500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>59800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>75700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>29000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>37400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>53900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>28900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1900</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V89" s="3">
+      <c r="V89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W89" s="3">
         <v>26400</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,76 +5937,80 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1200</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-300</v>
       </c>
       <c r="P91" s="3">
         <v>-300</v>
       </c>
       <c r="Q91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-700</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V91" s="3">
+      <c r="V91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,76 +6148,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-12900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-14500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-11500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-184300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2200</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V94" s="3">
+      <c r="V94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W94" s="3">
         <v>1300</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6248,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6024,35 +6258,35 @@
         <v>-13500</v>
       </c>
       <c r="E96" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="F96" s="3">
         <v>-13300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-28300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-12600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-12900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-12300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-12200</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-9100</v>
       </c>
       <c r="L96" s="3">
         <v>-9100</v>
       </c>
       <c r="M96" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="N96" s="3">
         <v>-5600</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
@@ -6083,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,208 +6530,220 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-13800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-9500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-44000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-42100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-60700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-43400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-74200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>77600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-30500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-32800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>19400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-26600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-21800</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V100" s="3">
+      <c r="V100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W100" s="3">
         <v>-10500</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-3000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1300</v>
-      </c>
-      <c r="P101" s="3">
-        <v>-100</v>
       </c>
       <c r="Q101" s="3">
         <v>-100</v>
       </c>
       <c r="R101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-200</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
-      <c r="W101" s="3" t="s">
-        <v>4</v>
+      <c r="V101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W101" s="3">
+        <v>0</v>
       </c>
       <c r="X101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>48900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>37200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-10100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-19500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-39100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-46600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>38700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>29200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>69100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-26200</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V102" s="3">
+      <c r="V102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W102" s="3">
         <v>17200</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/STEP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STEP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
   <si>
     <t>STEP</t>
   </si>
@@ -656,327 +656,340 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>187800</v>
+      </c>
+      <c r="E8" s="3">
         <v>357900</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3">
         <v>192800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>178600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>173100</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3">
         <v>366500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>412300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>284200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>311000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>360400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>249500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>243600</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V8" s="3">
+      <c r="V8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W8" s="3">
         <v>131900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>99600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>44700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E9" s="3">
         <v>11400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>15400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>9100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>11700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>41700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>89800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>102400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>101000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>110900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>144600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>83900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>83300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>40100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>40200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>24500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>167000</v>
+      </c>
+      <c r="E10" s="3">
         <v>346500</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="F10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="3">
         <v>191100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>169500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>160300</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" s="3">
         <v>276700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>309900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>183200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>200100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>215800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>165600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>160300</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V10" s="3">
+      <c r="V10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W10" s="3">
         <v>91700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>75100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>39400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>60200</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,8 +1015,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1073,8 +1087,11 @@
       <c r="Y12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,43 +1161,46 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3">
         <v>-100</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
         <v>-2700</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1215,16 +1235,19 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E15" s="3">
         <v>10400</v>
-      </c>
-      <c r="E15" s="3">
-        <v>10700</v>
       </c>
       <c r="F15" s="3">
         <v>10700</v>
@@ -1233,7 +1256,7 @@
         <v>10700</v>
       </c>
       <c r="H15" s="3">
-        <v>10900</v>
+        <v>10700</v>
       </c>
       <c r="I15" s="3">
         <v>10900</v>
@@ -1245,19 +1268,19 @@
         <v>10900</v>
       </c>
       <c r="L15" s="3">
+        <v>10900</v>
+      </c>
+      <c r="M15" s="3">
         <v>11100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>11000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>600</v>
-      </c>
-      <c r="P15" s="3">
-        <v>800</v>
       </c>
       <c r="Q15" s="3">
         <v>800</v>
@@ -1269,25 +1292,28 @@
         <v>800</v>
       </c>
       <c r="T15" s="3">
+        <v>800</v>
+      </c>
+      <c r="U15" s="3">
         <v>12700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>12200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1336,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>139300</v>
+      </c>
+      <c r="E17" s="3">
         <v>269200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>19200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>130300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>121200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>100200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>-104200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>-68400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>273300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>292700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>173400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>173700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>205100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>136400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>133100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>-15100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>91700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>51600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>84300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>67000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>41200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>51600</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>48600</v>
+      </c>
+      <c r="E18" s="3">
         <v>88700</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="F18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G18" s="3">
         <v>62500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>57400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>72900</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3">
         <v>93200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>119600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>110800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>137300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>155300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>113100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>110500</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W18" s="3">
         <v>47600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>32600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>17800</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,130 +1512,134 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E20" s="3">
         <v>8500</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="3">
         <v>6600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3700</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L20" s="3">
-        <v>23100</v>
+      <c r="L20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M20" s="3">
         <v>23100</v>
       </c>
       <c r="N20" s="3">
+        <v>23100</v>
+      </c>
+      <c r="O20" s="3">
         <v>3000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>7600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>4000</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W20" s="3">
         <v>2400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>69200</v>
+      </c>
+      <c r="E21" s="3">
         <v>108600</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="3">
+      <c r="F21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G21" s="3">
         <v>81100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>72000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>81300</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3">
         <v>128000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>154300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>116300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>142100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>164200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>118400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>115900</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1612,56 +1649,59 @@
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X21" s="3">
         <v>36000</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z21" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2600</v>
+        <v>3000</v>
       </c>
       <c r="E22" s="3">
         <v>2600</v>
       </c>
       <c r="F22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="G22" s="3">
         <v>2100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>600</v>
-      </c>
-      <c r="L22" s="3">
-        <v>500</v>
       </c>
       <c r="M22" s="3">
         <v>500</v>
       </c>
       <c r="N22" s="3">
+        <v>500</v>
+      </c>
+      <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
@@ -1669,22 +1709,22 @@
         <v>0</v>
       </c>
       <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>5300</v>
-      </c>
-      <c r="S22" s="3">
-        <v>4100</v>
       </c>
       <c r="T22" s="3">
         <v>4100</v>
       </c>
       <c r="U22" s="3">
+        <v>4100</v>
+      </c>
+      <c r="V22" s="3">
         <v>2400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2600</v>
-      </c>
-      <c r="W22" s="3">
-        <v>2700</v>
       </c>
       <c r="X22" s="3">
         <v>2700</v>
@@ -1692,150 +1732,159 @@
       <c r="Y22" s="3">
         <v>2700</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>54800</v>
+      </c>
+      <c r="E23" s="3">
         <v>94500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-24100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>67000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>58000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>67500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-14300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-74500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-20200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>115800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>142100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>113700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>140900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>162900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>116900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>109300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-51200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>51500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>18200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>47400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>31600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E24" s="3">
         <v>12000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>8600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>10700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-7400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>12200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>15800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-14100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>14400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>11700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>9500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1954,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E26" s="3">
         <v>82500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-23400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>59300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>49400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>56800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-13600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-67100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-21500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>103600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>126300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>127900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>126500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>151200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>107400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>108400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-52400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>50200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>17200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>46400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>31000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>15500</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E27" s="3">
         <v>30800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-20200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>26200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>21300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>28800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-29200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-11000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>41800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>48300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>62100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>41700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>37800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>25600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-800</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
       <c r="T27" s="3">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3">
         <v>-84900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>12100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>44400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>28500</v>
       </c>
-      <c r="X27" s="3">
-        <v>0</v>
-      </c>
       <c r="Y27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2176,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2250,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2324,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,150 +2398,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-8500</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" s="3">
         <v>-6600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3700</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L32" s="3">
-        <v>-23100</v>
+      <c r="L32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M32" s="3">
         <v>-23100</v>
       </c>
       <c r="N32" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="O32" s="3">
         <v>-3000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-4000</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W32" s="3">
         <v>-2400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E33" s="3">
         <v>30800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-20200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>26200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>21300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>28800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-29200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-11000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>41800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>48300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>62100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>41700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>37800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>25600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-800</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3">
         <v>-84900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>12100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>44400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>28500</v>
       </c>
-      <c r="X33" s="3">
-        <v>0</v>
-      </c>
       <c r="Y33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2620,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E35" s="3">
         <v>30800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-20200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>26200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>21300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>28800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-29200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-11000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>41800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>48300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>62100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>41700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>37800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>25600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-800</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3">
         <v>-84900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>12100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>44400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>28500</v>
       </c>
-      <c r="X35" s="3">
-        <v>0</v>
-      </c>
       <c r="Y35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2803,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,68 +2831,69 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>195400</v>
+      </c>
+      <c r="E41" s="3">
         <v>181600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>173600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>176100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>127200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>128600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>140100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>143600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>106400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>116400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>135900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>175000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>218600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>179900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>185000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>156900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>90700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>89900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>116100</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2816,8 +2903,11 @@
       <c r="Y41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2887,68 +2977,71 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2105000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2109500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1958400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2128500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2131800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2096600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2093800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2228300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2583900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2868600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2702700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2469100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1121500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>936100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>669900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>518900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>369300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>495600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>426500</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2958,8 +3051,11 @@
       <c r="Y43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3029,8 +3125,11 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3100,8 +3199,11 @@
       <c r="Y45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3171,68 +3273,71 @@
       <c r="Y46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>303700</v>
+      </c>
+      <c r="E47" s="3">
         <v>266900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>236600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>198200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>161300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>145800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>123400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>107000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>108100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>107000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>98800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>90300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>82900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>74400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>63400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>57900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>50400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>53400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>49600</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>4</v>
       </c>
@@ -3242,50 +3347,53 @@
       <c r="Y47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>95400</v>
+      </c>
+      <c r="E48" s="3">
         <v>97800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>97400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>99800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>100500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>101100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>104800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>62800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>72100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>61100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>63300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>65500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>64700</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3301,8 +3409,8 @@
       <c r="U48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
+      <c r="V48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
@@ -3313,68 +3421,71 @@
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>875200</v>
+      </c>
+      <c r="E49" s="3">
         <v>885400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>895800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>913900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>924500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>935200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>946100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>956900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>967800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>978700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>992400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1003100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>12300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>13100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>14000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>14800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>15600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>16600</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3384,8 +3495,11 @@
       <c r="Y49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3569,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,68 +3643,71 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>196200</v>
+      </c>
+      <c r="E52" s="3">
         <v>185200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>46100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>37500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>39600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>45300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>50200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>40400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>32500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>28900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>20000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>98500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>93400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>39600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>47200</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T52" s="3">
+      <c r="T52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U52" s="3">
         <v>700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>600</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3597,8 +3717,11 @@
       <c r="Y52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,68 +3791,71 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3834400</v>
+      </c>
+      <c r="E54" s="3">
         <v>3788800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3468200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3608400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3530800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3497400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3503100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3575600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3906200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4188100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4036600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3831500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1622800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1320800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>994800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>817700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>549400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>680800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>631500</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3739,8 +3865,11 @@
       <c r="Y54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3895,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,68 +3923,69 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>102800</v>
+      </c>
+      <c r="E57" s="3">
         <v>96400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>78300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>66400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>66300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>67800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>64700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>63600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>55400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>61500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>41500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>48900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>24800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>33800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>28400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>29300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>25400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>36000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>40900</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3864,8 +3995,11 @@
       <c r="Y57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3935,68 +4069,71 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1588600</v>
+      </c>
+      <c r="E59" s="3">
         <v>1637800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1574300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1687600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1670500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1655800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1725400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1787000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2023600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2220400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2095800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1917900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>815600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>613400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>418700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>350400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>213000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>264500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>238900</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4006,8 +4143,11 @@
       <c r="Y59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4077,47 +4217,50 @@
       <c r="Y60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>172100</v>
+      </c>
+      <c r="E61" s="3">
         <v>148800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>123700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>123600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>98500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>98400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>83200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>63100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>63000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>62900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>62800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>112600</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -4128,17 +4271,17 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>143000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>143100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>143300</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4148,8 +4291,11 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4195,21 +4341,21 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>4</v>
+      <c r="R62" s="3">
+        <v>0</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T62" s="3">
+      <c r="T62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U62" s="3">
         <v>200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>400</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4219,8 +4365,11 @@
       <c r="Y62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4439,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4513,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,68 +4587,71 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3467400</v>
+      </c>
+      <c r="E66" s="3">
         <v>3464300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2706300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2813700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2764800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2725800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2751400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2814400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3106400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3370500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3260900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3147900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1317800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1071400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>848600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>698200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>414200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>464600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>444900</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4503,8 +4661,11 @@
       <c r="Y66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4691,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4763,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4837,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4743,8 +4911,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,59 +4985,62 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E72" s="3">
         <v>13800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>131300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>165200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>152600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>160400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>144500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>164000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>205900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>229600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>197200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>158100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>99100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>60400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>24800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-800</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4885,8 +5059,11 @@
       <c r="Y72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5133,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5207,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,68 +5281,71 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>366900</v>
+      </c>
+      <c r="E76" s="3">
         <v>324500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>761800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>794700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>766000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>771600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>751700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>761200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>799800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>817600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>775700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>683600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>304900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>249400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>146200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>119600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>135200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>216200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>186600</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>4</v>
       </c>
@@ -5169,8 +5355,11 @@
       <c r="Y76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5429,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E81" s="3">
         <v>30800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-20200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>26200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>21300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>28800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-29200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-11000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>41800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>48300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>62100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>41700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>37800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>25600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-800</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3">
         <v>-84900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>12100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>44400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>28500</v>
       </c>
-      <c r="X81" s="3">
-        <v>0</v>
-      </c>
       <c r="Y81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,52 +5612,53 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E83" s="3">
         <v>11500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>12200</v>
-      </c>
-      <c r="F83" s="3">
-        <v>12000</v>
       </c>
       <c r="G83" s="3">
         <v>12000</v>
       </c>
       <c r="H83" s="3">
-        <v>12100</v>
+        <v>12000</v>
       </c>
       <c r="I83" s="3">
         <v>12100</v>
       </c>
       <c r="J83" s="3">
+        <v>12100</v>
+      </c>
+      <c r="K83" s="3">
         <v>11700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>11500</v>
-      </c>
-      <c r="L83" s="3">
-        <v>11700</v>
       </c>
       <c r="M83" s="3">
         <v>11700</v>
       </c>
       <c r="N83" s="3">
+        <v>11700</v>
+      </c>
+      <c r="O83" s="3">
         <v>2400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1300</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>1400</v>
       </c>
       <c r="R83" s="3">
         <v>1400</v>
@@ -5468,25 +5667,28 @@
         <v>1400</v>
       </c>
       <c r="T83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="U83" s="3">
         <v>1600</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X83" s="3">
         <v>1700</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5758,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5832,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5906,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5980,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,79 +6054,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>50200</v>
+      </c>
+      <c r="E89" s="3">
         <v>7600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>25200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>71100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>57600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>88200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>57500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>32300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>46500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>59800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>75700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>29000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>37400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>53900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>28900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1900</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X89" s="3">
         <v>26400</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,79 +6158,83 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1200</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-300</v>
       </c>
       <c r="Q91" s="3">
         <v>-300</v>
       </c>
       <c r="R91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S91" s="3">
         <v>-400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-700</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6304,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,79 +6378,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-9100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-10900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-12900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-14500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-11500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-184300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2200</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X94" s="3">
         <v>1300</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,47 +6482,48 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-13500</v>
+        <v>-23800</v>
       </c>
       <c r="E96" s="3">
         <v>-13500</v>
       </c>
       <c r="F96" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="G96" s="3">
         <v>-13300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-28300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-12600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-12900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-12300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-12200</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-9100</v>
       </c>
       <c r="M96" s="3">
         <v>-9100</v>
       </c>
       <c r="N96" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="O96" s="3">
         <v>-5600</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
@@ -6320,8 +6554,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6628,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6702,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,217 +6776,229 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-22900</v>
+      </c>
+      <c r="E100" s="3">
         <v>9300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-13800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-9500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-44000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-42100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-60700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-43400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-74200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>77600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-30500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-32800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-5300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>19400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-26600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-21800</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X100" s="3">
         <v>-10500</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1300</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-100</v>
       </c>
       <c r="R101" s="3">
         <v>-100</v>
       </c>
       <c r="S101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-200</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
-      <c r="X101" s="3" t="s">
-        <v>4</v>
+      <c r="W101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X101" s="3">
+        <v>0</v>
       </c>
       <c r="Y101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E102" s="3">
         <v>8000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>48900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-11500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>37200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-10100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-19500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-39100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-46600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>38700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>29200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>69100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-26200</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X102" s="3">
         <v>17200</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/STEP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STEP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
   <si>
     <t>STEP</t>
   </si>
@@ -656,141 +656,145 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>187800</v>
+        <v>271700</v>
       </c>
       <c r="E8" s="3">
-        <v>357900</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G8" s="3">
-        <v>192800</v>
+        <v>186400</v>
+      </c>
+      <c r="F8" s="3">
+        <v>356800</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H8" s="3">
-        <v>178600</v>
+        <v>191400</v>
       </c>
       <c r="I8" s="3">
-        <v>173100</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>4</v>
+        <v>178000</v>
+      </c>
+      <c r="J8" s="3">
+        <v>172400</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>4</v>
@@ -798,198 +802,207 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N8" s="3">
         <v>366500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>412300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>284200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>311000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>360400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>249500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>243600</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W8" s="3">
+      <c r="W8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X8" s="3">
         <v>131900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>99600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>44700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>20800</v>
+        <v>170600</v>
       </c>
       <c r="E9" s="3">
-        <v>11400</v>
+        <v>98200</v>
       </c>
       <c r="F9" s="3">
-        <v>15400</v>
+        <v>216600</v>
       </c>
       <c r="G9" s="3">
-        <v>1700</v>
+        <v>-29400</v>
       </c>
       <c r="H9" s="3">
-        <v>9100</v>
+        <v>98600</v>
       </c>
       <c r="I9" s="3">
-        <v>12800</v>
+        <v>87900</v>
       </c>
       <c r="J9" s="3">
+        <v>66300</v>
+      </c>
+      <c r="K9" s="3">
         <v>11700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>41700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>89800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>102400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>101000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>110900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>144600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>83900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>83300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>40100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>40200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>24500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>167000</v>
+        <v>101000</v>
       </c>
       <c r="E10" s="3">
-        <v>346500</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>4</v>
+        <v>88200</v>
+      </c>
+      <c r="F10" s="3">
+        <v>140200</v>
       </c>
       <c r="G10" s="3">
-        <v>191100</v>
+        <v>14800</v>
       </c>
       <c r="H10" s="3">
-        <v>169500</v>
+        <v>92800</v>
       </c>
       <c r="I10" s="3">
+        <v>90100</v>
+      </c>
+      <c r="J10" s="3">
+        <v>106000</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="3">
+        <v>276700</v>
+      </c>
+      <c r="O10" s="3">
+        <v>309900</v>
+      </c>
+      <c r="P10" s="3">
+        <v>183200</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>200100</v>
+      </c>
+      <c r="R10" s="3">
+        <v>215800</v>
+      </c>
+      <c r="S10" s="3">
+        <v>165600</v>
+      </c>
+      <c r="T10" s="3">
         <v>160300</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M10" s="3">
-        <v>276700</v>
-      </c>
-      <c r="N10" s="3">
-        <v>309900</v>
-      </c>
-      <c r="O10" s="3">
-        <v>183200</v>
-      </c>
-      <c r="P10" s="3">
-        <v>200100</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>215800</v>
-      </c>
-      <c r="R10" s="3">
-        <v>165600</v>
-      </c>
-      <c r="S10" s="3">
-        <v>160300</v>
-      </c>
-      <c r="T10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X10" s="3">
         <v>91700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>75100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>39400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>60200</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1016,8 +1029,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1090,8 +1104,11 @@
       <c r="Z12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,46 +1181,49 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>14800</v>
       </c>
       <c r="E14" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
+        <v>4100</v>
+      </c>
+      <c r="F14" s="3">
+        <v>10900</v>
+      </c>
+      <c r="G14" s="3">
+        <v>15200</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1500</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K14" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J14" s="3">
+        <v>6600</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3">
         <v>-2700</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1238,31 +1258,34 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>10500</v>
+        <v>11400</v>
       </c>
       <c r="E15" s="3">
-        <v>10400</v>
+        <v>11300</v>
       </c>
       <c r="F15" s="3">
-        <v>10700</v>
+        <v>11500</v>
       </c>
       <c r="G15" s="3">
-        <v>10700</v>
+        <v>11600</v>
       </c>
       <c r="H15" s="3">
-        <v>10700</v>
+        <v>11300</v>
       </c>
       <c r="I15" s="3">
-        <v>10900</v>
+        <v>11400</v>
       </c>
       <c r="J15" s="3">
-        <v>10900</v>
+        <v>11400</v>
       </c>
       <c r="K15" s="3">
         <v>10900</v>
@@ -1271,19 +1294,19 @@
         <v>10900</v>
       </c>
       <c r="M15" s="3">
+        <v>10900</v>
+      </c>
+      <c r="N15" s="3">
         <v>11100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>11000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>600</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>800</v>
       </c>
       <c r="R15" s="3">
         <v>800</v>
@@ -1295,25 +1318,28 @@
         <v>800</v>
       </c>
       <c r="U15" s="3">
+        <v>800</v>
+      </c>
+      <c r="V15" s="3">
         <v>12700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>12200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,105 +1363,109 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>139300</v>
+        <v>209900</v>
       </c>
       <c r="E17" s="3">
-        <v>269200</v>
+        <v>136400</v>
       </c>
       <c r="F17" s="3">
-        <v>19200</v>
+        <v>258300</v>
       </c>
       <c r="G17" s="3">
-        <v>130300</v>
+        <v>9000</v>
       </c>
       <c r="H17" s="3">
-        <v>121200</v>
+        <v>132700</v>
       </c>
       <c r="I17" s="3">
-        <v>100200</v>
+        <v>122500</v>
       </c>
       <c r="J17" s="3">
+        <v>101800</v>
+      </c>
+      <c r="K17" s="3">
         <v>5200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>-104200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>-68400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>273300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>292700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>173400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>173700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>205100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>136400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>133100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>-15100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>91700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>51600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>84300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>67000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>41200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>51600</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>48600</v>
+        <v>61800</v>
       </c>
       <c r="E18" s="3">
-        <v>88700</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>4</v>
+        <v>50000</v>
+      </c>
+      <c r="F18" s="3">
+        <v>98500</v>
       </c>
       <c r="G18" s="3">
-        <v>62500</v>
+        <v>-23600</v>
       </c>
       <c r="H18" s="3">
-        <v>57400</v>
+        <v>58700</v>
       </c>
       <c r="I18" s="3">
-        <v>72900</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>4</v>
+        <v>55500</v>
+      </c>
+      <c r="J18" s="3">
+        <v>70500</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>4</v>
@@ -1443,50 +1473,53 @@
       <c r="L18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="3">
         <v>93200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>119600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>110800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>137300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>155300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>113100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>110500</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X18" s="3">
         <v>47600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>32600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>17800</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,31 +1546,32 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>9300</v>
+        <v>-1200</v>
       </c>
       <c r="E20" s="3">
-        <v>8500</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>4</v>
+        <v>400</v>
+      </c>
+      <c r="F20" s="3">
+        <v>1300</v>
       </c>
       <c r="G20" s="3">
-        <v>6600</v>
+        <v>-5200</v>
       </c>
       <c r="H20" s="3">
-        <v>2700</v>
+        <v>900</v>
       </c>
       <c r="I20" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>4</v>
+        <v>-200</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>4</v>
@@ -1545,73 +1579,76 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M20" s="3">
-        <v>23100</v>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N20" s="3">
         <v>23100</v>
       </c>
       <c r="O20" s="3">
+        <v>23100</v>
+      </c>
+      <c r="P20" s="3">
         <v>3000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>7600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>4000</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X20" s="3">
         <v>2400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>69200</v>
+        <v>74300</v>
       </c>
       <c r="E21" s="3">
+        <v>61000</v>
+      </c>
+      <c r="F21" s="3">
         <v>108600</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G21" s="3">
-        <v>81100</v>
+        <v>-6900</v>
       </c>
       <c r="H21" s="3">
-        <v>72000</v>
+        <v>69100</v>
       </c>
       <c r="I21" s="3">
-        <v>81300</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
+        <v>67200</v>
+      </c>
+      <c r="J21" s="3">
+        <v>81900</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>4</v>
@@ -1619,30 +1656,30 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N21" s="3">
         <v>128000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>154300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>116300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>142100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>164200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>118400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>115900</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1652,59 +1689,62 @@
       <c r="W21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y21" s="3">
         <v>36000</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA21" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E22" s="3">
         <v>3000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>2600</v>
       </c>
       <c r="F22" s="3">
         <v>2600</v>
       </c>
       <c r="G22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H22" s="3">
         <v>2100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>600</v>
-      </c>
-      <c r="M22" s="3">
-        <v>500</v>
       </c>
       <c r="N22" s="3">
         <v>500</v>
       </c>
       <c r="O22" s="3">
+        <v>500</v>
+      </c>
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
@@ -1712,22 +1752,22 @@
         <v>0</v>
       </c>
       <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
         <v>5300</v>
-      </c>
-      <c r="T22" s="3">
-        <v>4100</v>
       </c>
       <c r="U22" s="3">
         <v>4100</v>
       </c>
       <c r="V22" s="3">
+        <v>4100</v>
+      </c>
+      <c r="W22" s="3">
         <v>2400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2600</v>
-      </c>
-      <c r="X22" s="3">
-        <v>2700</v>
       </c>
       <c r="Y22" s="3">
         <v>2700</v>
@@ -1735,156 +1775,165 @@
       <c r="Z22" s="3">
         <v>2700</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>57900</v>
+      </c>
+      <c r="E23" s="3">
         <v>54800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>94500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-24100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>67000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>58000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>67500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-14300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-74500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-20200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>115800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>142100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>113700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>140900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>162900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>116900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>109300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-51200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>51500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>18200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>47400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>31600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E24" s="3">
         <v>6800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>12000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>10700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-7400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>12200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>15800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-14100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>14400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>11700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>9500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2006,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>53100</v>
+      </c>
+      <c r="E26" s="3">
         <v>48000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>82500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-23400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>59300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>49400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>56800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-13600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-67100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-21500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>103600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>126300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>127900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>126500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>151200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>107400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>108400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-52400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>50200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>17200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>46400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>31000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>15500</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E27" s="3">
         <v>13300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>30800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-20200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>26200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>21300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>28800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-29200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-11000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>41800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>48300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>62100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>41700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>37800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>25600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-800</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
       <c r="U27" s="3">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3">
         <v>-84900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>12100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>44400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>28500</v>
       </c>
-      <c r="Y27" s="3">
-        <v>0</v>
-      </c>
       <c r="Z27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2237,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2253,8 +2314,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2391,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,31 +2468,34 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-9300</v>
+        <v>1200</v>
       </c>
       <c r="E32" s="3">
-        <v>-8500</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>4</v>
+        <v>-400</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-1300</v>
       </c>
       <c r="G32" s="3">
-        <v>-6600</v>
+        <v>5200</v>
       </c>
       <c r="H32" s="3">
-        <v>-2700</v>
+        <v>-900</v>
       </c>
       <c r="I32" s="3">
-        <v>3700</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>4</v>
+        <v>200</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>4</v>
@@ -2433,124 +2503,130 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M32" s="3">
-        <v>-23100</v>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N32" s="3">
         <v>-23100</v>
       </c>
       <c r="O32" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="P32" s="3">
         <v>-3000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-7600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-4000</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X32" s="3">
         <v>-2400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E33" s="3">
         <v>13300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>30800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-20200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>26200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>21300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>28800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-29200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-11000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>41800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>48300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>62100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>41700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>37800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>25600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-800</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
       <c r="U33" s="3">
+        <v>0</v>
+      </c>
+      <c r="V33" s="3">
         <v>-84900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>12100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>44400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>28500</v>
       </c>
-      <c r="Y33" s="3">
-        <v>0</v>
-      </c>
       <c r="Z33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2699,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E35" s="3">
         <v>13300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>30800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-20200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>26200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>21300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>28800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-29200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-11000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>41800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>48300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>62100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>41700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>37800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>25600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-800</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
       <c r="U35" s="3">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3">
         <v>-84900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>12100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>44400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>28500</v>
       </c>
-      <c r="Y35" s="3">
-        <v>0</v>
-      </c>
       <c r="Z35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2889,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,71 +2918,72 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>224600</v>
+      </c>
+      <c r="E41" s="3">
         <v>195400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>181600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>173600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>176100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>127200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>128600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>140100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>143600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>106400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>116400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>135900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>175000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>218600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>179900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>185000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>156900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>90700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>89900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>116100</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2906,8 +2993,11 @@
       <c r="Z41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2980,71 +3070,74 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2105000</v>
+        <v>1529500</v>
       </c>
       <c r="E43" s="3">
-        <v>2109500</v>
+        <v>1487500</v>
       </c>
       <c r="F43" s="3">
-        <v>1958400</v>
+        <v>1478400</v>
       </c>
       <c r="G43" s="3">
-        <v>2128500</v>
+        <v>1326000</v>
       </c>
       <c r="H43" s="3">
-        <v>2131800</v>
+        <v>1428100</v>
       </c>
       <c r="I43" s="3">
-        <v>2096600</v>
+        <v>1386200</v>
       </c>
       <c r="J43" s="3">
+        <v>1325900</v>
+      </c>
+      <c r="K43" s="3">
         <v>2093800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2228300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2583900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2868600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2702700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2469100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1121500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>936100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>669900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>518900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>369300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>495600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>426500</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3054,31 +3147,34 @@
       <c r="Z43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3128,31 +3224,34 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -3202,31 +3301,34 @@
       <c r="Z45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>1754900</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>1683600</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>1660700</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>1500300</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>1604900</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>1514200</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>1455500</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -3276,71 +3378,74 @@
       <c r="Z46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>303700</v>
+        <v>1012800</v>
       </c>
       <c r="E47" s="3">
-        <v>266900</v>
+        <v>921300</v>
       </c>
       <c r="F47" s="3">
-        <v>236600</v>
+        <v>898100</v>
       </c>
       <c r="G47" s="3">
-        <v>198200</v>
+        <v>869000</v>
       </c>
       <c r="H47" s="3">
-        <v>161300</v>
+        <v>898700</v>
       </c>
       <c r="I47" s="3">
-        <v>145800</v>
+        <v>906900</v>
       </c>
       <c r="J47" s="3">
+        <v>916400</v>
+      </c>
+      <c r="K47" s="3">
         <v>123400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>107000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>108100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>107000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>98800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>90300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>82900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>74400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>63400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>57900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>50400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>53400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>49600</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>4</v>
       </c>
@@ -3350,53 +3455,56 @@
       <c r="Z47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>92800</v>
+      </c>
+      <c r="E48" s="3">
         <v>95400</v>
       </c>
-      <c r="E48" s="3">
-        <v>97800</v>
-      </c>
       <c r="F48" s="3">
+        <v>127300</v>
+      </c>
+      <c r="G48" s="3">
         <v>97400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>99800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>100500</v>
       </c>
-      <c r="I48" s="3">
-        <v>101100</v>
-      </c>
       <c r="J48" s="3">
+        <v>117000</v>
+      </c>
+      <c r="K48" s="3">
         <v>104800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>62800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>72100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>61100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>63300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>65500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>64700</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3412,8 +3520,8 @@
       <c r="V48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W48" s="3">
-        <v>0</v>
+      <c r="W48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X48" s="3">
         <v>0</v>
@@ -3424,71 +3532,74 @@
       <c r="Z48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>864900</v>
+      </c>
+      <c r="E49" s="3">
         <v>875200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>885400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>895800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>913900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>924500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>935200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>946100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>956900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>967800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>978700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>992400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1003100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>11700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>12300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>13100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>14000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>14800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>15600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>16600</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3498,8 +3609,11 @@
       <c r="Z49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3686,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,71 +3763,74 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>196200</v>
+        <v>69800</v>
       </c>
       <c r="E52" s="3">
-        <v>185200</v>
+        <v>63500</v>
       </c>
       <c r="F52" s="3">
-        <v>46100</v>
+        <v>32800</v>
       </c>
       <c r="G52" s="3">
-        <v>37500</v>
+        <v>60300</v>
       </c>
       <c r="H52" s="3">
+        <v>54200</v>
+      </c>
+      <c r="I52" s="3">
+        <v>45700</v>
+      </c>
+      <c r="J52" s="3">
+        <v>29000</v>
+      </c>
+      <c r="K52" s="3">
+        <v>50200</v>
+      </c>
+      <c r="L52" s="3">
+        <v>40400</v>
+      </c>
+      <c r="M52" s="3">
+        <v>32500</v>
+      </c>
+      <c r="N52" s="3">
+        <v>28900</v>
+      </c>
+      <c r="O52" s="3">
+        <v>20000</v>
+      </c>
+      <c r="P52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>98500</v>
+      </c>
+      <c r="R52" s="3">
+        <v>93400</v>
+      </c>
+      <c r="S52" s="3">
         <v>39600</v>
       </c>
-      <c r="I52" s="3">
-        <v>45300</v>
-      </c>
-      <c r="J52" s="3">
-        <v>50200</v>
-      </c>
-      <c r="K52" s="3">
-        <v>40400</v>
-      </c>
-      <c r="L52" s="3">
-        <v>32500</v>
-      </c>
-      <c r="M52" s="3">
-        <v>28900</v>
-      </c>
-      <c r="N52" s="3">
-        <v>20000</v>
-      </c>
-      <c r="O52" s="3">
-        <v>1700</v>
-      </c>
-      <c r="P52" s="3">
-        <v>98500</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>93400</v>
-      </c>
-      <c r="R52" s="3">
-        <v>39600</v>
-      </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>47200</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U52" s="3">
+      <c r="U52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V52" s="3">
         <v>700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>600</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3720,8 +3840,11 @@
       <c r="Z52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,71 +3917,74 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4039900</v>
+      </c>
+      <c r="E54" s="3">
         <v>3834400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3788800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3468200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3608400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3530800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3497400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3503100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3575600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3906200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4188100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4036600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3831500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1622800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1320800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>994800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>817700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>549400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>680800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>631500</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3868,8 +3994,11 @@
       <c r="Z54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4025,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,71 +4054,72 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>102800</v>
+        <v>21400</v>
       </c>
       <c r="E57" s="3">
-        <v>96400</v>
+        <v>26000</v>
       </c>
       <c r="F57" s="3">
-        <v>78300</v>
+        <v>22300</v>
       </c>
       <c r="G57" s="3">
-        <v>66400</v>
+        <v>37000</v>
       </c>
       <c r="H57" s="3">
-        <v>66300</v>
+        <v>34000</v>
       </c>
       <c r="I57" s="3">
-        <v>67800</v>
+        <v>31000</v>
       </c>
       <c r="J57" s="3">
+        <v>12600</v>
+      </c>
+      <c r="K57" s="3">
         <v>64700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>63600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>55400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>61500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>41500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>48900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>24800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>33800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>28400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>29300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>25400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>36000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>40900</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3998,28 +4129,31 @@
       <c r="Z57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>8400</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>12400</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>9100</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -4072,71 +4206,74 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1588600</v>
-      </c>
-      <c r="E59" s="3">
-        <v>1637800</v>
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F59" s="3">
-        <v>1574300</v>
+        <v>53700</v>
       </c>
       <c r="G59" s="3">
-        <v>1687600</v>
+        <v>400</v>
       </c>
       <c r="H59" s="3">
-        <v>1670500</v>
+        <v>800</v>
       </c>
       <c r="I59" s="3">
-        <v>1655800</v>
+        <v>1100</v>
       </c>
       <c r="J59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K59" s="3">
         <v>1725400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1787000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2023600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2220400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2095800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1917900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>815600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>613400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>418700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>350400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>213000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>264500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>238900</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4146,31 +4283,34 @@
       <c r="Z59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>1429100</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>1285500</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>1396500</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>1293800</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>1404800</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>1396100</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>1343000</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -4220,50 +4360,53 @@
       <c r="Z60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>172100</v>
+        <v>280100</v>
       </c>
       <c r="E61" s="3">
-        <v>148800</v>
+        <v>277800</v>
       </c>
       <c r="F61" s="3">
-        <v>123700</v>
+        <v>253200</v>
       </c>
       <c r="G61" s="3">
-        <v>123600</v>
+        <v>239500</v>
       </c>
       <c r="H61" s="3">
-        <v>98500</v>
+        <v>236700</v>
       </c>
       <c r="I61" s="3">
-        <v>98400</v>
+        <v>205500</v>
       </c>
       <c r="J61" s="3">
+        <v>219600</v>
+      </c>
+      <c r="K61" s="3">
         <v>83200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>63100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>63000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>62900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>62800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>112600</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -4274,17 +4417,17 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>143000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>143100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>143300</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4294,31 +4437,34 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>274100</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>281500</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>214300</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>244600</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>244000</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>234000</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>241400</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -4344,21 +4490,21 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>4</v>
+      <c r="S62" s="3">
+        <v>0</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U62" s="3">
+      <c r="U62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V62" s="3">
         <v>200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>400</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4368,8 +4514,11 @@
       <c r="Z62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4591,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4668,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,71 +4745,74 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3467400</v>
+        <v>2039600</v>
       </c>
       <c r="E66" s="3">
-        <v>3464300</v>
+        <v>1894900</v>
       </c>
       <c r="F66" s="3">
-        <v>2706300</v>
+        <v>1915700</v>
       </c>
       <c r="G66" s="3">
-        <v>2813700</v>
+        <v>1802300</v>
       </c>
       <c r="H66" s="3">
-        <v>2764800</v>
+        <v>1910700</v>
       </c>
       <c r="I66" s="3">
-        <v>2725800</v>
+        <v>1860600</v>
       </c>
       <c r="J66" s="3">
+        <v>1844100</v>
+      </c>
+      <c r="K66" s="3">
         <v>2751400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2814400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3106400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3370500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3260900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3147900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1317800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1071400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>848600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>698200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>414200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>464600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>444900</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4664,8 +4822,11 @@
       <c r="Z66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4853,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4928,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5005,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4914,8 +5082,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,62 +5159,65 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E72" s="3">
         <v>3000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>13800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>131300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>165200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>152600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>160400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>144500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>164000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>205900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>229600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>197200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>158100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>99100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>60400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>24800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-800</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>4</v>
       </c>
@@ -5062,8 +5236,11 @@
       <c r="Z72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5313,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5390,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,71 +5467,74 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>397500</v>
+      </c>
+      <c r="E76" s="3">
         <v>366900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>324500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>761800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>794700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>766000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>771600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>751700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>761200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>799800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>817600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>775700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>683600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>304900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>249400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>146200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>119600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>135200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>216200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>186600</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>4</v>
       </c>
@@ -5358,8 +5544,11 @@
       <c r="Z76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5621,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E81" s="3">
         <v>13300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>30800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-20200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>26200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>21300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>28800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-29200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-11000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>41800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>48300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>62100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>41700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>37800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>25600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-800</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
       <c r="U81" s="3">
+        <v>0</v>
+      </c>
+      <c r="V81" s="3">
         <v>-84900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>12100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>44400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>28500</v>
       </c>
-      <c r="Y81" s="3">
-        <v>0</v>
-      </c>
       <c r="Z81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,55 +5811,56 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>11300</v>
+        <v>700</v>
       </c>
       <c r="E83" s="3">
+        <v>700</v>
+      </c>
+      <c r="F83" s="3">
+        <v>500</v>
+      </c>
+      <c r="G83" s="3">
+        <v>600</v>
+      </c>
+      <c r="H83" s="3">
+        <v>700</v>
+      </c>
+      <c r="I83" s="3">
+        <v>600</v>
+      </c>
+      <c r="J83" s="3">
+        <v>600</v>
+      </c>
+      <c r="K83" s="3">
+        <v>12100</v>
+      </c>
+      <c r="L83" s="3">
+        <v>11700</v>
+      </c>
+      <c r="M83" s="3">
         <v>11500</v>
-      </c>
-      <c r="F83" s="3">
-        <v>12200</v>
-      </c>
-      <c r="G83" s="3">
-        <v>12000</v>
-      </c>
-      <c r="H83" s="3">
-        <v>12000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>12100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>12100</v>
-      </c>
-      <c r="K83" s="3">
-        <v>11700</v>
-      </c>
-      <c r="L83" s="3">
-        <v>11500</v>
-      </c>
-      <c r="M83" s="3">
-        <v>11700</v>
       </c>
       <c r="N83" s="3">
         <v>11700</v>
       </c>
       <c r="O83" s="3">
+        <v>11700</v>
+      </c>
+      <c r="P83" s="3">
         <v>2400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1300</v>
-      </c>
-      <c r="R83" s="3">
-        <v>1400</v>
       </c>
       <c r="S83" s="3">
         <v>1400</v>
@@ -5670,25 +5869,28 @@
         <v>1400</v>
       </c>
       <c r="U83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="V83" s="3">
         <v>1600</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X83" s="3">
+      <c r="X83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y83" s="3">
         <v>1700</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5963,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6040,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6117,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6194,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,82 +6271,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>53700</v>
+      </c>
+      <c r="E89" s="3">
         <v>50200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>25200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>71100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>57600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>88200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>57500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>32300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>46500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>59800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>75700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>29000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>37400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>53900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>28900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1900</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X89" s="3">
+      <c r="X89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y89" s="3">
         <v>26400</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,82 +6379,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1200</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-300</v>
       </c>
       <c r="R91" s="3">
         <v>-300</v>
       </c>
       <c r="S91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="T91" s="3">
         <v>-400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-700</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X91" s="3">
+      <c r="X91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6531,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,82 +6608,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-9100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-12900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-14500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-11500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-184300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2200</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X94" s="3">
+      <c r="X94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y94" s="3">
         <v>1300</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,50 +6716,51 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-23800</v>
+        <v>16200</v>
       </c>
       <c r="E96" s="3">
-        <v>-13500</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-13500</v>
+        <v>13900</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G96" s="3">
-        <v>-13300</v>
+        <v>13500</v>
       </c>
       <c r="H96" s="3">
-        <v>-28300</v>
+        <v>13200</v>
       </c>
       <c r="I96" s="3">
-        <v>-12600</v>
+        <v>12600</v>
       </c>
       <c r="J96" s="3">
+        <v>12600</v>
+      </c>
+      <c r="K96" s="3">
         <v>-12900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-12300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-12200</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-9100</v>
       </c>
       <c r="N96" s="3">
         <v>-9100</v>
       </c>
       <c r="O96" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="P96" s="3">
         <v>-5600</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -6557,8 +6791,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6868,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6945,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,226 +7022,238 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-22900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>9300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-13800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-9500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-44000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-42100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-60700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-43400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-74200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>77600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-30500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-32800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-5300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>19400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-26600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-21800</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X100" s="3">
+      <c r="X100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
-        <v>200</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-3000</v>
-      </c>
       <c r="G101" s="3">
-        <v>100</v>
+        <v>-1500</v>
       </c>
       <c r="H101" s="3">
-        <v>-700</v>
+        <v>800</v>
       </c>
       <c r="I101" s="3">
+        <v>700</v>
+      </c>
+      <c r="J101" s="3">
+        <v>400</v>
+      </c>
+      <c r="K101" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="L101" s="3">
+        <v>800</v>
+      </c>
+      <c r="M101" s="3">
+        <v>700</v>
+      </c>
+      <c r="N101" s="3">
+        <v>400</v>
+      </c>
+      <c r="O101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="P101" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="K101" s="3">
-        <v>800</v>
-      </c>
-      <c r="L101" s="3">
-        <v>700</v>
-      </c>
-      <c r="M101" s="3">
-        <v>400</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-600</v>
-      </c>
-      <c r="O101" s="3">
-        <v>400</v>
-      </c>
-      <c r="P101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1300</v>
-      </c>
-      <c r="R101" s="3">
-        <v>-100</v>
       </c>
       <c r="S101" s="3">
         <v>-100</v>
       </c>
       <c r="T101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-200</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y101" s="3" t="s">
-        <v>4</v>
+      <c r="X101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
       </c>
       <c r="Z101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E102" s="3">
         <v>13900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>8000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>48900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-11500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>37200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-10100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-19500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-39100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-46600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>38700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-5100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>29200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>69100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-26200</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X102" s="3">
+      <c r="X102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y102" s="3">
         <v>17200</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/STEP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STEP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="92">
   <si>
     <t>STEP</t>
   </si>
@@ -656,353 +656,365 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>339000</v>
+      </c>
+      <c r="E8" s="3">
         <v>271700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>186400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>356800</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3">
         <v>191400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>178000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>172400</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N8" s="3">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3">
         <v>366500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>412300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>284200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>311000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>360400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>249500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>243600</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X8" s="3">
+      <c r="X8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y8" s="3">
         <v>131900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>99600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>44700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>655400</v>
+      </c>
+      <c r="E9" s="3">
         <v>170600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>98200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>216600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>-29400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>98600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>87900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>66300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>11700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>41700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>89800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>102400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>101000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>110900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>144600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>83900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>83300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>40100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>40200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>24500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-316400</v>
+      </c>
+      <c r="E10" s="3">
         <v>101000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>88200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>140200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>14800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>92800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>90100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>106000</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" s="3">
         <v>276700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>309900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>183200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>200100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>215800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>165600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>160300</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X10" s="3">
+      <c r="X10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y10" s="3">
         <v>91700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>75100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>39400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>60200</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1030,8 +1042,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1107,8 +1120,11 @@
       <c r="AA12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,49 +1200,52 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E14" s="3">
         <v>14800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>4100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>10900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>15200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>6600</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
         <v>-2700</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1261,8 +1280,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1270,25 +1292,25 @@
         <v>11400</v>
       </c>
       <c r="E15" s="3">
+        <v>11400</v>
+      </c>
+      <c r="F15" s="3">
         <v>11300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>11500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>11600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>11300</v>
-      </c>
-      <c r="I15" s="3">
-        <v>11400</v>
       </c>
       <c r="J15" s="3">
         <v>11400</v>
       </c>
       <c r="K15" s="3">
-        <v>10900</v>
+        <v>11400</v>
       </c>
       <c r="L15" s="3">
         <v>10900</v>
@@ -1297,19 +1319,19 @@
         <v>10900</v>
       </c>
       <c r="N15" s="3">
+        <v>10900</v>
+      </c>
+      <c r="O15" s="3">
         <v>11100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>11000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>600</v>
-      </c>
-      <c r="R15" s="3">
-        <v>800</v>
       </c>
       <c r="S15" s="3">
         <v>800</v>
@@ -1321,25 +1343,28 @@
         <v>800</v>
       </c>
       <c r="V15" s="3">
+        <v>800</v>
+      </c>
+      <c r="W15" s="3">
         <v>12700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>12200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>696100</v>
+      </c>
+      <c r="E17" s="3">
         <v>209900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>136400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>258300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>132700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>122500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>101800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>-104200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>-68400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>273300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>292700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>173400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>173700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>205100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>136400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>133100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>-15100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>91700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>51600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>84300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>67000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>41200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>51600</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-357100</v>
+      </c>
+      <c r="E18" s="3">
         <v>61800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>50000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>98500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-23600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>58700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>55500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>70500</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3">
         <v>93200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>119600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>110800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>137300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>155300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>113100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>110500</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y18" s="3">
         <v>47600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>32600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>17800</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,34 +1579,35 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-5200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>4</v>
+      <c r="K20" s="3">
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>4</v>
@@ -1582,107 +1615,110 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N20" s="3">
-        <v>23100</v>
+      <c r="N20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O20" s="3">
         <v>23100</v>
       </c>
       <c r="P20" s="3">
+        <v>23100</v>
+      </c>
+      <c r="Q20" s="3">
         <v>3000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>7600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>4000</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y20" s="3">
         <v>2400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-348200</v>
+      </c>
+      <c r="E21" s="3">
         <v>74300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>61000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>108600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-6900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>69100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>67200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>81900</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3">
         <v>128000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>154300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>116300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>142100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>164200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>118400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>115900</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1692,62 +1728,65 @@
       <c r="X21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z21" s="3">
         <v>36000</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB21" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E22" s="3">
         <v>3500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>2600</v>
       </c>
       <c r="G22" s="3">
         <v>2600</v>
       </c>
       <c r="H22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="I22" s="3">
         <v>2100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>600</v>
-      </c>
-      <c r="N22" s="3">
-        <v>500</v>
       </c>
       <c r="O22" s="3">
         <v>500</v>
       </c>
       <c r="P22" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -1755,22 +1794,22 @@
         <v>0</v>
       </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>5300</v>
-      </c>
-      <c r="U22" s="3">
-        <v>4100</v>
       </c>
       <c r="V22" s="3">
         <v>4100</v>
       </c>
       <c r="W22" s="3">
+        <v>4100</v>
+      </c>
+      <c r="X22" s="3">
         <v>2400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2600</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>2700</v>
       </c>
       <c r="Z22" s="3">
         <v>2700</v>
@@ -1778,162 +1817,171 @@
       <c r="AA22" s="3">
         <v>2700</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-344700</v>
+      </c>
+      <c r="E23" s="3">
         <v>57900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>54800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>94500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-24100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>67000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>58000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>67500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-14300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-74500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-20200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>115800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>142100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>113700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>140900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>162900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>116900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>109300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-51200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>51500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>18200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>47400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>31600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-57600</v>
+      </c>
+      <c r="E24" s="3">
         <v>4800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>12000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>8600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>10700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-7400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>12200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>15800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-14100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>14400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>11700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>9500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-287200</v>
+      </c>
+      <c r="E26" s="3">
         <v>53100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>48000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>82500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-23400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>59300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>49400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>56800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-13600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-67100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-21500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>103600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>126300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>127900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>126500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>151200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>107400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>108400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-52400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>50200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>17200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>46400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>31000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>15500</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-192000</v>
+      </c>
+      <c r="E27" s="3">
         <v>17600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>13300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>30800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-20200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>26200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>21300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>28800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-6900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-29200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-11000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>41800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>48300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>62100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>41700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>37800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>25600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-800</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
       <c r="V27" s="3">
+        <v>0</v>
+      </c>
+      <c r="W27" s="3">
         <v>-84900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>12100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>44400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>28500</v>
       </c>
-      <c r="Z27" s="3">
-        <v>0</v>
-      </c>
       <c r="AA27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2317,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,34 +2537,37 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E32" s="3">
         <v>1200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>5200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>4</v>
+      <c r="K32" s="3">
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>4</v>
@@ -2506,127 +2575,133 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N32" s="3">
-        <v>-23100</v>
+      <c r="N32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O32" s="3">
         <v>-23100</v>
       </c>
       <c r="P32" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-7600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-4000</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-192000</v>
+      </c>
+      <c r="E33" s="3">
         <v>17600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>13300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>30800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-20200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>26200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>21300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>28800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-6900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-29200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-11000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>41800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>48300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>62100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>41700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>37800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>25600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-800</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
       <c r="V33" s="3">
+        <v>0</v>
+      </c>
+      <c r="W33" s="3">
         <v>-84900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>12100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>44400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>28500</v>
       </c>
-      <c r="Z33" s="3">
-        <v>0</v>
-      </c>
       <c r="AA33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-192000</v>
+      </c>
+      <c r="E35" s="3">
         <v>17600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>13300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>30800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-20200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>26200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>21300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>28800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-6900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-29200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-11000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>41800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>48300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>62100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>41700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>37800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>25600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-800</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
       <c r="V35" s="3">
+        <v>0</v>
+      </c>
+      <c r="W35" s="3">
         <v>-84900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>12100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>44400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>28500</v>
       </c>
-      <c r="Z35" s="3">
-        <v>0</v>
-      </c>
       <c r="AA35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,74 +3004,75 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>278800</v>
+      </c>
+      <c r="E41" s="3">
         <v>224600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>195400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>181600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>173600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>176100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>127200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>128600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>140100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>143600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>106400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>116400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>135900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>175000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>218600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>179900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>185000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>156900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>90700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>89900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>116100</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2996,8 +3082,11 @@
       <c r="AA41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3073,74 +3162,77 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1634700</v>
+      </c>
+      <c r="E43" s="3">
         <v>1529500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1487500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1478400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1326000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1428100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1386200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1325900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2093800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2228300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2583900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2868600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2702700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2469100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1121500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>936100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>669900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>518900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>369300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>495600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>426500</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3150,8 +3242,11 @@
       <c r="AA43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3176,8 +3271,8 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3227,8 +3322,11 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3253,8 +3351,8 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -3304,35 +3402,38 @@
       <c r="AA45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1914200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1754900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1683600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1660700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1500300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1604900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1514200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1455500</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -3381,74 +3482,77 @@
       <c r="AA46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1065700</v>
+      </c>
+      <c r="E47" s="3">
         <v>1012800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>921300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>898100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>869000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>898700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>906900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>916400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>123400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>107000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>108100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>107000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>98800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>90300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>82900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>74400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>63400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>57900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>50400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>53400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>49600</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>4</v>
       </c>
@@ -3458,56 +3562,59 @@
       <c r="AA47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>90600</v>
+      </c>
+      <c r="E48" s="3">
         <v>92800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>95400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>127300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>97400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>99800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>100500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>117000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>104800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>62800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>72100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>61100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>63300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>65500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>64700</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3523,8 +3630,8 @@
       <c r="W48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X48" s="3">
-        <v>0</v>
+      <c r="X48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y48" s="3">
         <v>0</v>
@@ -3535,74 +3642,77 @@
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>854700</v>
+      </c>
+      <c r="E49" s="3">
         <v>864900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>875200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>885400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>895800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>913900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>924500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>935200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>946100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>956900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>967800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>978700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>992400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1003100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>11700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>12300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>13100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>14000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>14800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>15600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>16600</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3612,8 +3722,11 @@
       <c r="AA49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,74 +3882,77 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>68400</v>
+      </c>
+      <c r="E52" s="3">
         <v>69800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>63500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>32800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>60300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>54200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>45700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>29000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>50200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>40400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>32500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>28900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>20000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>98500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>93400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>39600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>47200</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V52" s="3">
+      <c r="V52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W52" s="3">
         <v>700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>600</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3843,8 +3962,11 @@
       <c r="AA52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,74 +4042,77 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4349600</v>
+      </c>
+      <c r="E54" s="3">
         <v>4039900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3834400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3788800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3468200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3608400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3530800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3497400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3503100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3575600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3906200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4188100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4036600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3831500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1622800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1320800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>994800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>817700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>549400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>680800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>631500</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3997,8 +4122,11 @@
       <c r="AA54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,74 +4184,75 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>139100</v>
+      </c>
+      <c r="E57" s="3">
         <v>21400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>26000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>22300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>37000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>34000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>31000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>12600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>64700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>63600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>55400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>61500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>41500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>48900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>24800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>33800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>28400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>29300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>25400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>36000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>40900</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>4</v>
       </c>
@@ -4132,32 +4262,35 @@
       <c r="AA57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E58" s="3">
         <v>8400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>15400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>9100</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -4209,74 +4342,77 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" s="3">
         <v>53700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1725400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1787000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2023600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2220400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2095800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1917900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>815600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>613400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>418700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>350400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>213000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>264500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>238900</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4286,35 +4422,38 @@
       <c r="AA59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2003600</v>
+      </c>
+      <c r="E60" s="3">
         <v>1429100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1285500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1396500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1293800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1404800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1396100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1343000</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -4363,53 +4502,56 @@
       <c r="AA60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>277000</v>
+      </c>
+      <c r="E61" s="3">
         <v>280100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>277800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>253200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>239500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>236700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>205500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>219600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>83200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>63100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>63000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>62900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>62800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>112600</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -4420,17 +4562,17 @@
         <v>0</v>
       </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>143000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>143100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>143300</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4440,35 +4582,38 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>325600</v>
+      </c>
+      <c r="E62" s="3">
         <v>274100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>281500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>214300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>244600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>244000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>234000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>241400</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -4493,21 +4638,21 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>4</v>
+      <c r="T62" s="3">
+        <v>0</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V62" s="3">
+      <c r="V62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W62" s="3">
         <v>200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>400</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4517,8 +4662,11 @@
       <c r="AA62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,74 +4902,77 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2606200</v>
+      </c>
+      <c r="E66" s="3">
         <v>2039600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1894900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1915700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1802300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1910700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1860600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1844100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2751400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2814400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3106400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3370500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3260900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3147900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1317800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1071400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>848600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>698200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>414200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>464600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>444900</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4825,8 +4982,11 @@
       <c r="AA66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5085,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,65 +5332,68 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-205700</v>
+      </c>
+      <c r="E72" s="3">
         <v>4000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>13800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>131300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>165200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>152600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>160400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>144500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>164000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>205900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>229600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>197200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>158100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>99100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>60400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>24800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-800</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>4</v>
       </c>
@@ -5239,8 +5412,11 @@
       <c r="AA72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,74 +5652,77 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>209800</v>
+      </c>
+      <c r="E76" s="3">
         <v>397500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>366900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>324500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>761800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>794700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>766000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>771600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>751700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>761200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>799800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>817600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>775700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>683600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>304900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>249400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>146200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>119600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>135200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>216200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>186600</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>4</v>
       </c>
@@ -5547,8 +5732,11 @@
       <c r="AA76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-192000</v>
+      </c>
+      <c r="E81" s="3">
         <v>17600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>13300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>30800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-20200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>26200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>21300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>28800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-6900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-29200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-11000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>41800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>48300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>62100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>41700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>37800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>25600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-800</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
       <c r="V81" s="3">
+        <v>0</v>
+      </c>
+      <c r="W81" s="3">
         <v>-84900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>12100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>44400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>28500</v>
       </c>
-      <c r="Z81" s="3">
-        <v>0</v>
-      </c>
       <c r="AA81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB81" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,58 +6009,59 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="E83" s="3">
         <v>700</v>
       </c>
       <c r="F83" s="3">
+        <v>700</v>
+      </c>
+      <c r="G83" s="3">
         <v>500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>700</v>
-      </c>
-      <c r="I83" s="3">
-        <v>600</v>
       </c>
       <c r="J83" s="3">
         <v>600</v>
       </c>
       <c r="K83" s="3">
+        <v>600</v>
+      </c>
+      <c r="L83" s="3">
         <v>12100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>11700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>11500</v>
-      </c>
-      <c r="N83" s="3">
-        <v>11700</v>
       </c>
       <c r="O83" s="3">
         <v>11700</v>
       </c>
       <c r="P83" s="3">
+        <v>11700</v>
+      </c>
+      <c r="Q83" s="3">
         <v>2400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1300</v>
-      </c>
-      <c r="S83" s="3">
-        <v>1400</v>
       </c>
       <c r="T83" s="3">
         <v>1400</v>
@@ -5872,25 +6070,28 @@
         <v>1400</v>
       </c>
       <c r="V83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="W83" s="3">
         <v>1600</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z83" s="3">
         <v>1700</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,85 +6487,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E89" s="3">
         <v>53700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>50200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>25200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>71100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>57600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>88200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>57500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>32300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>46500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>59800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>75700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>29000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>37400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>53900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>28900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1900</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z89" s="3">
         <v>26400</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,85 +6599,89 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1200</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-300</v>
       </c>
       <c r="S91" s="3">
         <v>-300</v>
       </c>
       <c r="T91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="U91" s="3">
         <v>-400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-700</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,85 +6837,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-20900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-9100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-12900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-14500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-11500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-184300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2200</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z94" s="3">
         <v>1300</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,53 +6949,54 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E96" s="3">
         <v>16200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>13900</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G96" s="3">
-        <v>13500</v>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H96" s="3">
+        <v>13400</v>
+      </c>
+      <c r="I96" s="3">
         <v>13200</v>
-      </c>
-      <c r="I96" s="3">
-        <v>12600</v>
       </c>
       <c r="J96" s="3">
         <v>12600</v>
       </c>
       <c r="K96" s="3">
+        <v>12600</v>
+      </c>
+      <c r="L96" s="3">
         <v>-12900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-12300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-12200</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-9100</v>
       </c>
       <c r="O96" s="3">
         <v>-9100</v>
       </c>
       <c r="P96" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -6794,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,235 +7267,247 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>26200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-22900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>9300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-13800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-9500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-44000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-42100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-60700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-43400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-74200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>77600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-30500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-32800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-5300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>19400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-26600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-21800</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-10500</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1300</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-100</v>
       </c>
       <c r="T101" s="3">
         <v>-100</v>
       </c>
       <c r="U101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-200</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z101" s="3" t="s">
-        <v>4</v>
+      <c r="Y101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
       </c>
       <c r="AA101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>54100</v>
+      </c>
+      <c r="E102" s="3">
         <v>29200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>13900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>8000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>48900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-11500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>37200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-10100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-19500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-39100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-46600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>38700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-5100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>29200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>69100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-26200</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z102" s="3">
         <v>17200</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/STEP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STEP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
   <si>
     <t>STEP</t>
   </si>
@@ -656,365 +656,391 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>364300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>377700</v>
+      </c>
+      <c r="F8" s="3">
         <v>339000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>271700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>186400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>356800</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K8" s="3">
         <v>191400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>178000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>172400</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3">
         <v>366500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>412300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>284200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>311000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>360400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>249500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>243600</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Y8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA8" s="3">
         <v>131900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>99600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>44700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>380400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>340800</v>
+      </c>
+      <c r="F9" s="3">
         <v>655400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>170600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>98200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>216600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>-29400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>98600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>87900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>66300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>11700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>13600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>41700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>89800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>102400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>101000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>110900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>144600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>83900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>83300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>2900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>40100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>1300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>40200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>24500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>5300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>36900</v>
+      </c>
+      <c r="F10" s="3">
         <v>-316400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>101000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>88200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>140200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>14800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>92800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>90100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>106000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3">
         <v>276700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>309900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>183200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>200100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>215800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>165600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>160300</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA10" s="3">
         <v>91700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>75100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>39400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>60200</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1043,8 +1069,10 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1123,8 +1151,14 @@
       <c r="AB12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,55 +1237,61 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F14" s="3">
         <v>2000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>14800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>4100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>10900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>15200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>1500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>1600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>6600</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3">
         <v>-2700</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1283,8 +1323,14 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1295,49 +1341,49 @@
         <v>11400</v>
       </c>
       <c r="F15" s="3">
+        <v>11400</v>
+      </c>
+      <c r="G15" s="3">
+        <v>11400</v>
+      </c>
+      <c r="H15" s="3">
         <v>11300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>11500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>11600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>11300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>11400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>11400</v>
-      </c>
-      <c r="L15" s="3">
-        <v>10900</v>
-      </c>
-      <c r="M15" s="3">
-        <v>10900</v>
       </c>
       <c r="N15" s="3">
         <v>10900</v>
       </c>
       <c r="O15" s="3">
+        <v>10900</v>
+      </c>
+      <c r="P15" s="3">
+        <v>10900</v>
+      </c>
+      <c r="Q15" s="3">
         <v>11100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>11000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>1900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>600</v>
-      </c>
-      <c r="S15" s="3">
-        <v>800</v>
-      </c>
-      <c r="T15" s="3">
-        <v>800</v>
       </c>
       <c r="U15" s="3">
         <v>800</v>
@@ -1346,25 +1392,31 @@
         <v>800</v>
       </c>
       <c r="W15" s="3">
+        <v>800</v>
+      </c>
+      <c r="X15" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y15" s="3">
         <v>12700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>12200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>1400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>1300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>1200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1442,182 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>423200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>384000</v>
+      </c>
+      <c r="F17" s="3">
         <v>696100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>209900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>136400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>258300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>9000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>132700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>122500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>101800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>5200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>-104200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>-68400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>273300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>292700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>173400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>173700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>205100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>136400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>133100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>-15100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>91700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>51600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>84300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>67000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>41200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>51600</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-58900</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-357100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>61800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>50000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>98500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-23600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>58700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>55500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>70500</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3">
         <v>93200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>119600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>110800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>137300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>155300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>113100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>110500</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA18" s="3">
         <v>47600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>32600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>3500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>17800</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,408 +1646,440 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E20" s="3">
+        <v>31000</v>
+      </c>
+      <c r="F20" s="3">
         <v>2500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-1200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>1300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-5200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>4</v>
+      <c r="M20" s="3">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3">
         <v>23100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>23100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>3000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>3700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>7600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>3900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>4000</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA20" s="3">
         <v>2400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>1800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>1400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-42400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-348200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>74300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>61000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>108600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-6900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>69100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>67200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>81900</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3">
         <v>128000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>154300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>116300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>142100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>164200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>118400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>115900</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB21" s="3">
         <v>36000</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD21" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="E22" s="3">
-        <v>3500</v>
+        <v>3200</v>
       </c>
       <c r="F22" s="3">
         <v>3000</v>
       </c>
       <c r="G22" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I22" s="3">
         <v>2600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>2600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>2100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>2000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>1700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>1100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
       <c r="T22" s="3">
         <v>0</v>
       </c>
       <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
         <v>5300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>4100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>4100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>2400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>2600</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>2700</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>2700</v>
       </c>
       <c r="AB22" s="3">
         <v>2700</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-20400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-344700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>57900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>54800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>94500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-24100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>67000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>58000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>67500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-14300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-74500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-20200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>115800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>142100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>113700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>140900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>162900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>116900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>109300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-51200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>51500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>18200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>47400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>31600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>2200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F24" s="3">
         <v>-57600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>4800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>6800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>12000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>7700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>8600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>10700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-7400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>1300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>12200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>15800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-14100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>14400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>11700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>9500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>1200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>1300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>1000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>1100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2158,186 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>13200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-287200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>53100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>48000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>82500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-23400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>59300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>49400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>56800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-13600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-67100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-21500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>103600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>126300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>127900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>126500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>151200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>107400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>108400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-52400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>50200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>17200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>46400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>31000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>1800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>15500</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-38400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-192000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>17600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>13300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>30800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-20200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>26200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>21300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>28800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-6900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-29200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-11000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>41800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>48300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>62100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>41700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>37800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>25600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-800</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-84900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>12100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>44400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>28500</v>
       </c>
-      <c r="AA27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2416,14 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2380,8 +2502,14 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2588,14 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,168 +2674,186 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>1200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-1300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>5200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>4</v>
+      <c r="M32" s="3">
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-23100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-23100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-3000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-3700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-7600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-3900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-4000</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-38400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-192000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>17600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>13300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>30800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-20200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>26200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>21300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>28800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-6900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-29200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-11000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>41800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>48300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>62100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>41700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>37800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>25600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-800</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-84900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>12100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>44400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>28500</v>
       </c>
-      <c r="AA33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2932,191 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-38400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-192000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>17600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>13300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>30800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-20200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>26200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>21300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>28800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-6900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-29200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-11000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>41800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>48300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>62100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>41700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>37800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>25600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-800</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-84900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>12100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>44400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>28500</v>
       </c>
-      <c r="AA35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3145,10 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,88 +3177,96 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>244100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>289300</v>
+      </c>
+      <c r="F41" s="3">
         <v>278800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>224600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>195400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>181600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>173600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>176100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>127200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>128600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>140100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>143600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>106400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>116400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>135900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>175000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>218600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>179900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>185000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>156900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>90700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>89900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>116100</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3165,88 +3345,100 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1780900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1669300</v>
+      </c>
+      <c r="F43" s="3">
         <v>1634700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1529500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1487500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1478400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1326000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1428100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1386200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1325900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>2093800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>2228300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2583900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>2868600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>2702700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>2469100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1121500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>936100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>669900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>518900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>369300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>495600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>426500</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3274,11 +3466,11 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3325,8 +3517,14 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3354,11 +3552,11 @@
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
-      <c r="M45" s="3">
-        <v>0</v>
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N45" s="3">
         <v>0</v>
@@ -3405,41 +3603,47 @@
       <c r="AB45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2025600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1959100</v>
+      </c>
+      <c r="F46" s="3">
         <v>1914200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1754900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1683600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1660700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1500300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1604900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1514200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1455500</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -3485,142 +3689,154 @@
       <c r="AB46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1359800</v>
+      </c>
+      <c r="E47" s="3">
+        <v>1227900</v>
+      </c>
+      <c r="F47" s="3">
         <v>1065700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>1012800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>921300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>898100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>869000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>898700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>906900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>916400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>123400</v>
-      </c>
-      <c r="M47" s="3">
-        <v>107000</v>
-      </c>
-      <c r="N47" s="3">
-        <v>108100</v>
       </c>
       <c r="O47" s="3">
         <v>107000</v>
       </c>
       <c r="P47" s="3">
+        <v>108100</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>107000</v>
+      </c>
+      <c r="R47" s="3">
         <v>98800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>90300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>82900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>74400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>63400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>57900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>50400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>53400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>49600</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA47" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>89100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>121600</v>
+      </c>
+      <c r="F48" s="3">
         <v>90600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>92800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>95400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>127300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>97400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>99800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>100500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>117000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>104800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>62800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>72100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>61100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>63300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>65500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>64700</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3633,11 +3849,11 @@
       <c r="X48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y48" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>0</v>
+      <c r="Y48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA48" s="3">
         <v>0</v>
@@ -3645,88 +3861,100 @@
       <c r="AB48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>834200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>844400</v>
+      </c>
+      <c r="F49" s="3">
         <v>854700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>864900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>875200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>885400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>895800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>913900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>924500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>935200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>946100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>956900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>967800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>978700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>992400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>1003100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>11700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>12300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>13100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>14000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>14800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>15600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>16600</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA49" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +4033,14 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,88 +4119,100 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>70400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>50800</v>
+      </c>
+      <c r="F52" s="3">
         <v>68400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>69800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>63500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>32800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>60300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>54200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>45700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>29000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>50200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>40400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>32500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>28900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>20000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>1700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>98500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>93400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>39600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>47200</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y52" s="3">
         <v>700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>600</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,88 +4291,100 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4782400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>4586700</v>
+      </c>
+      <c r="F54" s="3">
         <v>4349600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>4039900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>3834400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>3788800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>3468200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>3608400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>3530800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>3497400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>3503100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>3575600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>3906200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>4188100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>4036600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>3831500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1622800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1320800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>994800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>817700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>549400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>680800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>631500</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4413,10 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,118 +4445,126 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>35800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>40200</v>
+      </c>
+      <c r="F57" s="3">
         <v>139100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>21400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>26000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>22300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>37000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>34000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>31000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>12600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>64700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>63600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>55400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>61500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>41500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>48900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>24800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>33800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>28400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>29300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>25400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>36000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>40900</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>17000</v>
+      </c>
+      <c r="F58" s="3">
         <v>4100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>8400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>12400</v>
       </c>
-      <c r="G58" s="3">
-        <v>15400</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>2700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>6000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>9100</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4345,121 +4613,133 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E59" s="3">
-        <v>0</v>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3">
         <v>53700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1725400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1787000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2023600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>2220400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>2095800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1917900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>815600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>613400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>418700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>350400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>213000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>264500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>238900</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2323400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2047600</v>
+      </c>
+      <c r="F60" s="3">
         <v>2003600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1429100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1285500</v>
       </c>
-      <c r="G60" s="3">
-        <v>1396500</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
+        <v>1381100</v>
+      </c>
+      <c r="J60" s="3">
         <v>1293800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1404800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1396100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1343000</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -4505,59 +4785,65 @@
       <c r="AB60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>369000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>365800</v>
+      </c>
+      <c r="F61" s="3">
         <v>277000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>280100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>277800</v>
       </c>
-      <c r="G61" s="3">
-        <v>253200</v>
-      </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
+        <v>268600</v>
+      </c>
+      <c r="J61" s="3">
         <v>239500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>236700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>205500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>219600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>83200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>63100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>63000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>62900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>62800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>112600</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4565,61 +4851,67 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>143000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>143100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>143300</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>344300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>349400</v>
+      </c>
+      <c r="F62" s="3">
         <v>325600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>274100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>281500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>214300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>244600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>244000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>234000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>241400</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
@@ -4641,32 +4933,38 @@
       <c r="T62" s="3">
         <v>0</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W62" s="3">
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y62" s="3">
         <v>200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>400</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +5043,14 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +5129,14 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,88 +5215,100 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3085000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2812300</v>
+      </c>
+      <c r="F66" s="3">
         <v>2606200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2039600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1894900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1915700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1802300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1910700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1860600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1844100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>2751400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>2814400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>3106400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>3370500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>3260900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>3147900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1317800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1071400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>848600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>698200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>414200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>464600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>444900</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5337,10 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5419,14 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5505,14 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5591,14 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,71 +5677,77 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-332000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-242500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-205700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>4000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>3000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>13800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>131300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>165200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>152600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>160400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>144500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>164000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>205900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>229600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>197200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>158100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>99100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>60400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>24800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-800</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>4</v>
       </c>
@@ -5415,8 +5763,14 @@
       <c r="AB72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5849,14 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5935,14 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,88 +6021,100 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>153900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>179400</v>
+      </c>
+      <c r="F76" s="3">
         <v>209800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>397500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>366900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>324500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>761800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>794700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>766000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>771600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>751700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>761200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>799800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>817600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>775700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>683600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>304900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>249400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>146200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>119600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>135200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>216200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>186600</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6193,191 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-38400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-192000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>17600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>13300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>30800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-20200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>26200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>21300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>28800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-6900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-29200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-11000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>41800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>48300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>62100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>41700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>37800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>25600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-800</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-84900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>12100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>44400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>28500</v>
       </c>
-      <c r="AA81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD81" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,88 +6406,96 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F83" s="3">
         <v>900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>500</v>
-      </c>
-      <c r="H83" s="3">
-        <v>600</v>
-      </c>
-      <c r="I83" s="3">
-        <v>700</v>
       </c>
       <c r="J83" s="3">
         <v>600</v>
       </c>
       <c r="K83" s="3">
+        <v>700</v>
+      </c>
+      <c r="L83" s="3">
         <v>600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
+        <v>600</v>
+      </c>
+      <c r="N83" s="3">
         <v>12100</v>
-      </c>
-      <c r="M83" s="3">
-        <v>11700</v>
-      </c>
-      <c r="N83" s="3">
-        <v>11500</v>
       </c>
       <c r="O83" s="3">
         <v>11700</v>
       </c>
       <c r="P83" s="3">
+        <v>11500</v>
+      </c>
+      <c r="Q83" s="3">
         <v>11700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
+        <v>11700</v>
+      </c>
+      <c r="S83" s="3">
         <v>2400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>1200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>1300</v>
-      </c>
-      <c r="T83" s="3">
-        <v>1400</v>
-      </c>
-      <c r="U83" s="3">
-        <v>1400</v>
       </c>
       <c r="V83" s="3">
         <v>1400</v>
       </c>
       <c r="W83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="X83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Y83" s="3">
         <v>1600</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z83" s="3">
+      <c r="Z83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB83" s="3">
         <v>1700</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB83" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6574,14 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6660,14 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6746,14 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6832,14 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,88 +6918,100 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-66500</v>
+      </c>
+      <c r="F89" s="3">
         <v>27600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>53700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>50200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>7600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>25200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>71100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>57600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>6000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>88200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>57500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>32300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>46500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>59800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>75700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>29000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>37400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>53900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>28900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-1900</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z89" s="3">
+      <c r="Z89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB89" s="3">
         <v>26400</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB89" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,88 +7040,96 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-600</v>
+        <v>-1100</v>
       </c>
       <c r="E91" s="3">
-        <v>-1300</v>
+        <v>-2700</v>
       </c>
       <c r="F91" s="3">
         <v>-600</v>
       </c>
       <c r="G91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I91" s="3">
         <v>-900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-4100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-6800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-7800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-2500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1700</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-500</v>
       </c>
       <c r="P91" s="3">
         <v>-300</v>
       </c>
       <c r="Q91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="R91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-1200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-300</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-400</v>
       </c>
       <c r="V91" s="3">
         <v>-300</v>
       </c>
       <c r="W91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="X91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-700</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z91" s="3">
+      <c r="Z91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB91" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +7208,14 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,88 +7294,100 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="F94" s="3">
         <v>-2600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-20900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-13200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-9100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-10900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-12900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-14500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-7400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-6100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-9700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-7600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-8800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-11500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-184300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-5700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-2600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-2800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-4100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-1600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-2200</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="Z94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB94" s="3">
         <v>1300</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB94" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,59 +7416,61 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E96" s="3">
+        <v>18000</v>
+      </c>
+      <c r="F96" s="3">
         <v>17200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>16200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>13900</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>13400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
+        <v>13400</v>
+      </c>
+      <c r="K96" s="3">
         <v>13200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>12600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>12600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-12900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-12300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-12200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-9100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-5600</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
@@ -7030,8 +7498,14 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7584,14 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7670,14 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,244 +7756,268 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-72200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>84900</v>
+      </c>
+      <c r="F100" s="3">
         <v>26200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-22900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>9300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-13800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-9500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-44000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-3400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-1800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-42100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-60700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-43400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-74200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>77600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-30500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-32800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-5300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>19400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-26600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-21800</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="Z100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-10500</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB100" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>200</v>
+      </c>
+      <c r="F101" s="3">
         <v>-3000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-1500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-1500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>700</v>
-      </c>
-      <c r="O101" s="3">
-        <v>400</v>
-      </c>
-      <c r="P101" s="3">
-        <v>-600</v>
       </c>
       <c r="Q101" s="3">
         <v>400</v>
       </c>
       <c r="R101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="S101" s="3">
+        <v>400</v>
+      </c>
+      <c r="T101" s="3">
         <v>-200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>1300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-200</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>0</v>
+      <c r="Z101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-45100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>10300</v>
+      </c>
+      <c r="F102" s="3">
         <v>54100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>29200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>13900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>8000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-2500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>48900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-11500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-3500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>37200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-10100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-19500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-39100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-46600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>38700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-5100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>29200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>69100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-26200</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z102" s="3">
+      <c r="Z102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB102" s="3">
         <v>17200</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB102" s="3" t="s">
+      <c r="AC102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/STEP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STEP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
   <si>
     <t>STEP</t>
   </si>
@@ -656,404 +656,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>586500</v>
+      </c>
+      <c r="E8" s="3">
         <v>454200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>364300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>377700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>339000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>271700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>186400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>356800</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3">
         <v>191400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>178000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>172400</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R8" s="3">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3">
         <v>366500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>412300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>284200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>311000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>360400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>249500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>243600</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AB8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC8" s="3">
         <v>131900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>99600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>44700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>757100</v>
+      </c>
+      <c r="E9" s="3">
         <v>1131700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>380400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>340800</v>
       </c>
-      <c r="G9" s="3">
-        <v>655400</v>
-      </c>
       <c r="H9" s="3">
+        <v>655000</v>
+      </c>
+      <c r="I9" s="3">
         <v>170600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>98200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>216600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>-29400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>98600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>87900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>66300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>11700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>13600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>41700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>89800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>102400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>101000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>110900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>144600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>83900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>83300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>40100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>40200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>24500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-170600</v>
+      </c>
+      <c r="E10" s="3">
         <v>-677500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-16100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>36900</v>
       </c>
-      <c r="G10" s="3">
-        <v>-316400</v>
-      </c>
       <c r="H10" s="3">
+        <v>-316000</v>
+      </c>
+      <c r="I10" s="3">
         <v>101000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>88200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>140200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>14800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>92800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>90100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>106000</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="3">
         <v>276700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>309900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>183200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>200100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>215800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>165600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>160300</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AB10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC10" s="3">
         <v>91700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>75100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>39400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>60200</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1085,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1174,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1263,61 +1279,64 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>600</v>
+      </c>
+      <c r="E14" s="3">
         <v>1300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-3300</v>
       </c>
-      <c r="G14" s="3">
-        <v>2000</v>
-      </c>
       <c r="H14" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I14" s="3">
         <v>14900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>10900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>15200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>6600</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1352,16 +1371,19 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E15" s="3">
         <v>11500</v>
-      </c>
-      <c r="E15" s="3">
-        <v>11400</v>
       </c>
       <c r="F15" s="3">
         <v>11400</v>
@@ -1373,25 +1395,25 @@
         <v>11400</v>
       </c>
       <c r="I15" s="3">
+        <v>11400</v>
+      </c>
+      <c r="J15" s="3">
         <v>11300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>11500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>11600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>11300</v>
-      </c>
-      <c r="M15" s="3">
-        <v>11400</v>
       </c>
       <c r="N15" s="3">
         <v>11400</v>
       </c>
       <c r="O15" s="3">
-        <v>10900</v>
+        <v>11400</v>
       </c>
       <c r="P15" s="3">
         <v>10900</v>
@@ -1400,19 +1422,19 @@
         <v>10900</v>
       </c>
       <c r="R15" s="3">
+        <v>10900</v>
+      </c>
+      <c r="S15" s="3">
         <v>11100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>11000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>600</v>
-      </c>
-      <c r="V15" s="3">
-        <v>800</v>
       </c>
       <c r="W15" s="3">
         <v>800</v>
@@ -1424,25 +1446,28 @@
         <v>800</v>
       </c>
       <c r="Z15" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA15" s="3">
         <v>12700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>12200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>1400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>1300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>1200</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1471,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>807700</v>
+      </c>
+      <c r="E17" s="3">
         <v>1176900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>423200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>384000</v>
       </c>
-      <c r="G17" s="3">
-        <v>696100</v>
-      </c>
       <c r="H17" s="3">
+        <v>695600</v>
+      </c>
+      <c r="I17" s="3">
         <v>209800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>136400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>258300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>132700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>122500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>101800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>-104200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>-68400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>273300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>292700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>173400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>173700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>205100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>136400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>133100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>-15100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>91700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>51600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>84300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>67000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>41200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>51600</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-221200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-722700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-58900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-6200</v>
       </c>
-      <c r="G18" s="3">
-        <v>-357100</v>
-      </c>
       <c r="H18" s="3">
+        <v>-356600</v>
+      </c>
+      <c r="I18" s="3">
         <v>61900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>50000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>98500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-23600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>58700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>55500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>70500</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3">
         <v>93200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>119600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>110800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>137300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>155300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>113100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>110500</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC18" s="3">
         <v>47600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>32600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>17800</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1682,46 +1714,47 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>31000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>4</v>
+      <c r="O20" s="3">
+        <v>0</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>4</v>
@@ -1729,119 +1762,122 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R20" s="3">
-        <v>23100</v>
+      <c r="R20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S20" s="3">
         <v>23100</v>
       </c>
       <c r="T20" s="3">
+        <v>23100</v>
+      </c>
+      <c r="U20" s="3">
         <v>3000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>7600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>3900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>4000</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AB20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC20" s="3">
         <v>2400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-211100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-709200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-42400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-25900</v>
       </c>
-      <c r="G21" s="3">
-        <v>-348200</v>
-      </c>
       <c r="H21" s="3">
+        <v>-347700</v>
+      </c>
+      <c r="I21" s="3">
         <v>74400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>61000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>108600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>69100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>67200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>81900</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3">
         <v>128000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>154300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>116300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>142100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>164200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>118400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>115900</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1851,74 +1887,77 @@
       <c r="AB21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD21" s="3">
         <v>36000</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF21" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E22" s="3">
         <v>4400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>3500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>2600</v>
       </c>
       <c r="K22" s="3">
         <v>2600</v>
       </c>
       <c r="L22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="M22" s="3">
         <v>2100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>600</v>
-      </c>
-      <c r="R22" s="3">
-        <v>500</v>
       </c>
       <c r="S22" s="3">
         <v>500</v>
       </c>
       <c r="T22" s="3">
+        <v>500</v>
+      </c>
+      <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
       <c r="V22" s="3">
         <v>0</v>
       </c>
@@ -1926,22 +1965,22 @@
         <v>0</v>
       </c>
       <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
         <v>5300</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>4100</v>
       </c>
       <c r="Z22" s="3">
         <v>4100</v>
       </c>
       <c r="AA22" s="3">
+        <v>4100</v>
+      </c>
+      <c r="AB22" s="3">
         <v>2400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2600</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>2700</v>
       </c>
       <c r="AD22" s="3">
         <v>2700</v>
@@ -1949,186 +1988,195 @@
       <c r="AE22" s="3">
         <v>2700</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-194600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-675800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-20400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>10000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-344700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>57900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>54800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>94500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-24100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>67000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>58000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>67500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-14300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-74500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-20200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>115800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>142100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>113700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>140900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>162900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>116900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>109300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-51200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>51500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>18200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>47400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>31600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-32200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-8300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-3200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-57600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>12000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>8600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>10700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>12200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>15800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-14100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>14400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>11700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>9500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2216,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-162400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-575500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>13200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-287200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>53100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>48000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>82500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-23400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>59300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>49400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>56800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-13600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-67100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-21500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>103600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>126300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>127900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>126500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>151200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>107400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>108400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-52400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>50200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>17200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>46400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>31000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>15500</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-123500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-366100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-38400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-18500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-192000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>17600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>13300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>30800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-20200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>26200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>21300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>28800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-29200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-11000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>41800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>48300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>62100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>41700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>37800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>25600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-800</v>
       </c>
-      <c r="Y27" s="3">
-        <v>0</v>
-      </c>
       <c r="Z27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-84900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>12100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>44400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>28500</v>
       </c>
-      <c r="AD27" s="3">
-        <v>0</v>
-      </c>
       <c r="AE27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2483,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2572,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2661,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2750,46 +2816,49 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E32" s="3">
         <v>2000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-31000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
+      <c r="O32" s="3">
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>4</v>
@@ -2797,139 +2866,145 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R32" s="3">
-        <v>-23100</v>
+      <c r="R32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S32" s="3">
         <v>-23100</v>
       </c>
       <c r="T32" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="U32" s="3">
         <v>-3000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-7600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-3900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AB32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-123500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-366100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-38400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-18500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-192000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>17600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>13300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>30800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-20200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>26200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>21300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>28800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-29200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-11000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>41800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>48300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>62100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>41700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>37800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>25600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-800</v>
       </c>
-      <c r="Y33" s="3">
-        <v>0</v>
-      </c>
       <c r="Z33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-84900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>12100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>44400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>28500</v>
       </c>
-      <c r="AD33" s="3">
-        <v>0</v>
-      </c>
       <c r="AE33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3017,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-123500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-366100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-38400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-18500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-192000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>17600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>13300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>30800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-20200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>26200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>21300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>28800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-29200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-11000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>41800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>48300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>62100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>41700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>37800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>25600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-800</v>
       </c>
-      <c r="Y35" s="3">
-        <v>0</v>
-      </c>
       <c r="Z35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-84900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>12100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>44400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>28500</v>
       </c>
-      <c r="AD35" s="3">
-        <v>0</v>
-      </c>
       <c r="AE35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3233,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3266,86 +3351,87 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>377500</v>
+      </c>
+      <c r="E41" s="3">
         <v>366200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>244100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>289300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>278800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>224600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>195400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>181600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>173600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>176100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>127200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>128600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>140100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>143600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>106400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>116400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>135900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>175000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>218600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>179900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>185000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>156900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>90700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>89900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>116100</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3355,8 +3441,11 @@
       <c r="AE41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3444,86 +3533,89 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2250500</v>
+      </c>
+      <c r="E43" s="3">
         <v>1933000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1780900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1669300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1634700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1529500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1487500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1478400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1326000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1428100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1386200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1325900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2093800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2228300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2583900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2868600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2702700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2469100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1121500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>936100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>669900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>518900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>369300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>495600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>426500</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3533,8 +3625,11 @@
       <c r="AE43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3571,8 +3666,8 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3622,8 +3717,11 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3660,8 +3758,8 @@
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
+      <c r="O45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P45" s="3">
         <v>0</v>
@@ -3711,47 +3809,50 @@
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2628500</v>
+      </c>
+      <c r="E46" s="3">
         <v>2299700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2025600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1959100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1914200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1754900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1683600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1660700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1500300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1604900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1514200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1455500</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -3800,86 +3901,89 @@
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1068800</v>
+      </c>
+      <c r="E47" s="3">
         <v>1537500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1359800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1227900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1065700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1012800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>921300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>898100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>869000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>898700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>906900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>916400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>123400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>107000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>108100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>107000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>98800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>90300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>82900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>74400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>63400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>57900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>50400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>53400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>49600</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC47" s="3" t="s">
         <v>4</v>
       </c>
@@ -3889,68 +3993,71 @@
       <c r="AE47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>84000</v>
+      </c>
+      <c r="E48" s="3">
         <v>86600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>89100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>121600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>90600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>92800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>95400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>127300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>97400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>99800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>100500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>117000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>104800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>62800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>72100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>61100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>63300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>65500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>64700</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3966,8 +4073,8 @@
       <c r="AA48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB48" s="3">
-        <v>0</v>
+      <c r="AB48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC48" s="3">
         <v>0</v>
@@ -3978,86 +4085,89 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>813800</v>
+      </c>
+      <c r="E49" s="3">
         <v>824000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>834200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>844400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>854700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>864900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>875200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>885400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>895800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>913900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>924500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>935200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>946100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>956900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>967800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>978700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>992400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1003100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>11700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>12300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>13100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>14000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>14800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>15600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>16600</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC49" s="3" t="s">
         <v>4</v>
       </c>
@@ -4067,8 +4177,11 @@
       <c r="AE49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4156,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4245,86 +4361,89 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>62800</v>
+      </c>
+      <c r="E52" s="3">
         <v>60000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>70400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>50800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>68400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>69800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>63500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>32800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>60300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>54200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>45700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>29000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>50200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>40400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>32500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>28900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>20000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>98500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>93400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>39600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>47200</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z52" s="3">
+      <c r="Z52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA52" s="3">
         <v>700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>600</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>4</v>
       </c>
@@ -4334,8 +4453,11 @@
       <c r="AE52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4423,86 +4545,89 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5241500</v>
+      </c>
+      <c r="E54" s="3">
         <v>5332100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4782400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4586700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4349600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4039900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3834400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3788800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3468200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3608400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3530800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3497400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3503100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3575600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3906200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4188100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4036600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3831500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1622800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1320800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>994800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>817700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>549400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>680800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>631500</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>4</v>
       </c>
@@ -4512,8 +4637,11 @@
       <c r="AE54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4545,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4578,86 +4707,87 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>41100</v>
+      </c>
+      <c r="E57" s="3">
         <v>48500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>35800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>40200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>139100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>21400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>26000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>22300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>37000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>34000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>31000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>64700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>63600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>55400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>61500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>41500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>48900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>24800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>33800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>28400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>29300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>25400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>36000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>40900</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>4</v>
       </c>
@@ -4667,44 +4797,47 @@
       <c r="AE57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E58" s="3">
         <v>26200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>13000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>17000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>8400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>12400</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>2700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>9100</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
@@ -4756,8 +4889,11 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4773,69 +4909,69 @@
       <c r="G59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K59" s="3">
         <v>53700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1725400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1787000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2023600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2220400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2095800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1917900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>815600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>613400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>418700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>350400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>213000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>264500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>238900</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4845,47 +4981,50 @@
       <c r="AE59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3946700</v>
+      </c>
+      <c r="E60" s="3">
         <v>3337300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2323400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2047600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2003600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1429100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1285500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1381100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1293800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1404800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1396100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1343000</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -4934,65 +5073,68 @@
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>372400</v>
+      </c>
+      <c r="E61" s="3">
         <v>370700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>369000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>365800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>277000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>280100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>277800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>268600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>239500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>236700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>205500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>219600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>83200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>63100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>63000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>62900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>62800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>112600</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -5003,17 +5145,17 @@
         <v>0</v>
       </c>
       <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>143000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>143100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>143300</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
@@ -5023,47 +5165,50 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>356900</v>
+      </c>
+      <c r="E62" s="3">
         <v>353500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>344300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>349400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>325600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>274100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>281500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>214300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>244600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>244000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>234000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>241400</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
@@ -5088,21 +5233,21 @@
       <c r="W62" s="3">
         <v>0</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>4</v>
+      <c r="X62" s="3">
+        <v>0</v>
       </c>
       <c r="Y62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="Z62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA62" s="3">
         <v>200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>400</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>4</v>
       </c>
@@ -5112,8 +5257,11 @@
       <c r="AE62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5201,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5290,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5379,86 +5533,89 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4722000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4106300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3085000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2812300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2606200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2039600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1894900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1915700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1802300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1910700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1860600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1844100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2751400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2814400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3106400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3370500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3260900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3147900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1317800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1071400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>848600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>698200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>414200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>464600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>444900</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>4</v>
       </c>
@@ -5468,8 +5625,11 @@
       <c r="AE66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5501,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5590,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5679,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5768,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5857,77 +6027,80 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-866300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-720400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-332000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-242500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-205700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>13800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>131300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>165200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>152600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>160400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>144500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>164000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>205900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>229600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>197200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>158100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>99100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>60400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>24800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-800</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>4</v>
       </c>
@@ -5946,8 +6119,11 @@
       <c r="AE72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6035,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6124,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6213,86 +6395,89 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-378800</v>
+      </c>
+      <c r="E76" s="3">
         <v>-233500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>153900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>179400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>209800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>397500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>366900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>324500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>761800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>794700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>766000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>771600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>751700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>761200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>799800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>817600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>775700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>683600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>304900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>249400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>146200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>119600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>135200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>216200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>186600</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>4</v>
       </c>
@@ -6302,8 +6487,11 @@
       <c r="AE76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6391,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-123500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-366100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-38400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-18500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-192000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>17600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>13300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>30800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-20200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>26200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>21300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>28800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-29200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-11000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>41800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>48300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>62100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>41700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>37800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>25600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-800</v>
       </c>
-      <c r="Y81" s="3">
-        <v>0</v>
-      </c>
       <c r="Z81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-84900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>12100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>44400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>28500</v>
       </c>
-      <c r="AD81" s="3">
-        <v>0</v>
-      </c>
       <c r="AE81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF81" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6607,70 +6804,71 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E83" s="3">
         <v>1200</v>
-      </c>
-      <c r="E83" s="3">
-        <v>1000</v>
       </c>
       <c r="F83" s="3">
         <v>1000</v>
       </c>
       <c r="G83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H83" s="3">
         <v>900</v>
-      </c>
-      <c r="H83" s="3">
-        <v>700</v>
       </c>
       <c r="I83" s="3">
         <v>700</v>
       </c>
       <c r="J83" s="3">
+        <v>700</v>
+      </c>
+      <c r="K83" s="3">
         <v>500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>700</v>
-      </c>
-      <c r="M83" s="3">
-        <v>600</v>
       </c>
       <c r="N83" s="3">
         <v>600</v>
       </c>
       <c r="O83" s="3">
+        <v>600</v>
+      </c>
+      <c r="P83" s="3">
         <v>12100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>11700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>11500</v>
-      </c>
-      <c r="R83" s="3">
-        <v>11700</v>
       </c>
       <c r="S83" s="3">
         <v>11700</v>
       </c>
       <c r="T83" s="3">
+        <v>11700</v>
+      </c>
+      <c r="U83" s="3">
         <v>2400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1300</v>
-      </c>
-      <c r="W83" s="3">
-        <v>1400</v>
       </c>
       <c r="X83" s="3">
         <v>1400</v>
@@ -6679,25 +6877,28 @@
         <v>1400</v>
       </c>
       <c r="Z83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AA83" s="3">
         <v>1600</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AC83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD83" s="3">
         <v>1700</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6785,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6874,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6963,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7052,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7141,97 +7354,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E89" s="3">
         <v>16200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>46300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-66500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>27600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>53700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>50200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>7600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>25200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>71100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>57600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>88200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>57500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>32300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>46500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>59800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>75700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>29000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>37400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>53900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>28900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AC89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD89" s="3">
         <v>26400</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7263,97 +7482,101 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1200</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-300</v>
       </c>
       <c r="W91" s="3">
         <v>-300</v>
       </c>
       <c r="X91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-700</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AC91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-100</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7441,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7530,97 +7756,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-67300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-9800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-11800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-20900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-13200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-10900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-14500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-7600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-8800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-11500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-184300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AC94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD94" s="3">
         <v>1300</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7652,65 +7884,66 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E96" s="3">
         <v>22000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>18900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>18000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>17200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>16200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>13900</v>
-      </c>
-      <c r="J96" s="3">
-        <v>13400</v>
       </c>
       <c r="K96" s="3">
         <v>13400</v>
       </c>
       <c r="L96" s="3">
+        <v>13400</v>
+      </c>
+      <c r="M96" s="3">
         <v>13200</v>
-      </c>
-      <c r="M96" s="3">
-        <v>12600</v>
       </c>
       <c r="N96" s="3">
         <v>12600</v>
       </c>
       <c r="O96" s="3">
+        <v>12600</v>
+      </c>
+      <c r="P96" s="3">
         <v>-12900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-12300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-12200</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-9100</v>
       </c>
       <c r="S96" s="3">
         <v>-9100</v>
       </c>
       <c r="T96" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="U96" s="3">
         <v>-5600</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
@@ -7741,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7830,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7919,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8008,271 +8250,283 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>51800</v>
+      </c>
+      <c r="E100" s="3">
         <v>115600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-72200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>84900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>26200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-22900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>9300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-13800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-9500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-44000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-42100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-60700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-43400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-74200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>77600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-30500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-32800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-5300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>19400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-26600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-21800</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AC100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-10500</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-3000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1300</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-100</v>
       </c>
       <c r="X101" s="3">
         <v>-100</v>
       </c>
       <c r="Y101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z101" s="3">
         <v>100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-200</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD101" s="3" t="s">
-        <v>4</v>
+      <c r="AC101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>0</v>
       </c>
       <c r="AE101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E102" s="3">
         <v>122100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-45100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>54100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>29200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>13900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>8000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>48900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-11500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>37200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-10100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-19500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-39100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-46600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>38700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-5100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>29200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>69100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-26200</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AC102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD102" s="3">
         <v>17200</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/STEP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STEP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
   <si>
     <t>STEP</t>
   </si>
@@ -656,416 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>588600</v>
+      </c>
+      <c r="E8" s="3">
         <v>586500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>454200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>364300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>377700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>339000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>271700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>186400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>356800</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N8" s="3">
         <v>191400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>178000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>172400</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S8" s="3">
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T8" s="3">
         <v>366500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>412300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>284200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>311000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>360400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>249500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>243600</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AC8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD8" s="3">
         <v>131900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>99600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>44700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>560500</v>
+      </c>
+      <c r="E9" s="3">
         <v>757100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1131700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>380400</v>
       </c>
-      <c r="G9" s="3">
-        <v>340800</v>
-      </c>
       <c r="H9" s="3">
+        <v>340400</v>
+      </c>
+      <c r="I9" s="3">
         <v>655000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>170600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>98200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>216600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>-29400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>98600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>87900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>66300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>11700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>13600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>41700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>89800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>102400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>101000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>110900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>144600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>83900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>83300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>40100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>40200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>24500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>5300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E10" s="3">
         <v>-170600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-677500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-16100</v>
       </c>
-      <c r="G10" s="3">
-        <v>36900</v>
-      </c>
       <c r="H10" s="3">
+        <v>37300</v>
+      </c>
+      <c r="I10" s="3">
         <v>-316000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>101000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>88200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>140200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>14800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>92800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>90100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>106000</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S10" s="3">
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T10" s="3">
         <v>276700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>309900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>183200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>200100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>215800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>165600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>160300</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AC10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD10" s="3">
         <v>91700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>75100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>39400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>60200</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1111,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1190,8 +1204,11 @@
       <c r="AF12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,64 +1299,67 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
-        <v>-3300</v>
-      </c>
       <c r="H14" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="I14" s="3">
         <v>2500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>14900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>10900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>15200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>6600</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3">
         <v>-2700</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1374,8 +1394,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1383,10 +1406,10 @@
         <v>11400</v>
       </c>
       <c r="E15" s="3">
+        <v>11400</v>
+      </c>
+      <c r="F15" s="3">
         <v>11500</v>
-      </c>
-      <c r="F15" s="3">
-        <v>11400</v>
       </c>
       <c r="G15" s="3">
         <v>11400</v>
@@ -1398,25 +1421,25 @@
         <v>11400</v>
       </c>
       <c r="J15" s="3">
+        <v>11400</v>
+      </c>
+      <c r="K15" s="3">
         <v>11300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>11500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>11600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>11300</v>
-      </c>
-      <c r="N15" s="3">
-        <v>11400</v>
       </c>
       <c r="O15" s="3">
         <v>11400</v>
       </c>
       <c r="P15" s="3">
-        <v>10900</v>
+        <v>11400</v>
       </c>
       <c r="Q15" s="3">
         <v>10900</v>
@@ -1425,19 +1448,19 @@
         <v>10900</v>
       </c>
       <c r="S15" s="3">
+        <v>10900</v>
+      </c>
+      <c r="T15" s="3">
         <v>11100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>11000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>600</v>
-      </c>
-      <c r="W15" s="3">
-        <v>800</v>
       </c>
       <c r="X15" s="3">
         <v>800</v>
@@ -1449,25 +1472,28 @@
         <v>800</v>
       </c>
       <c r="AA15" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB15" s="3">
         <v>12700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>12200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>1400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>1300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>1200</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1523,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>608900</v>
+      </c>
+      <c r="E17" s="3">
         <v>807700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1176900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>423200</v>
       </c>
-      <c r="G17" s="3">
-        <v>384000</v>
-      </c>
       <c r="H17" s="3">
+        <v>383800</v>
+      </c>
+      <c r="I17" s="3">
         <v>695600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>209800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>136400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>258300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>132700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>122500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>101800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>-104200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>-68400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>273300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>292700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>173400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>173700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>205100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>136400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>133100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>-15100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>91700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>51600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>84300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>67000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>41200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>51600</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-221200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-722700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-58900</v>
       </c>
-      <c r="G18" s="3">
-        <v>-6200</v>
-      </c>
       <c r="H18" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="I18" s="3">
         <v>-356600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>61900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>50000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>98500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-23600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>58700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>55500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>70500</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T18" s="3">
         <v>93200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>119600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>110800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>137300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>155300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>113100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>110500</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD18" s="3">
         <v>47600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>32600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>17800</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,49 +1748,50 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E20" s="3">
         <v>1300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>31000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-200</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>4</v>
+      <c r="P20" s="3">
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>4</v>
@@ -1765,122 +1799,125 @@
       <c r="R20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S20" s="3">
-        <v>23100</v>
+      <c r="S20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T20" s="3">
         <v>23100</v>
       </c>
       <c r="U20" s="3">
+        <v>23100</v>
+      </c>
+      <c r="V20" s="3">
         <v>3000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>3700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>7600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>3900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>4000</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD20" s="3">
         <v>2400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-211100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-709200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-42400</v>
       </c>
-      <c r="G21" s="3">
-        <v>-25900</v>
-      </c>
       <c r="H21" s="3">
+        <v>-25700</v>
+      </c>
+      <c r="I21" s="3">
         <v>-347700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>74400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>61000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>108600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-6900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>69100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>67200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>81900</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T21" s="3">
         <v>128000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>154300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>116300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>142100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>164200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>118400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>115900</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1890,77 +1927,80 @@
       <c r="AC21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE21" s="3">
         <v>36000</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG21" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E22" s="3">
         <v>5100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>3000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>2600</v>
       </c>
       <c r="L22" s="3">
         <v>2600</v>
       </c>
       <c r="M22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="N22" s="3">
         <v>2100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>600</v>
-      </c>
-      <c r="S22" s="3">
-        <v>500</v>
       </c>
       <c r="T22" s="3">
         <v>500</v>
       </c>
       <c r="U22" s="3">
+        <v>500</v>
+      </c>
+      <c r="V22" s="3">
         <v>100</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
       <c r="W22" s="3">
         <v>0</v>
       </c>
@@ -1968,22 +2008,22 @@
         <v>0</v>
       </c>
       <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
         <v>5300</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>4100</v>
       </c>
       <c r="AA22" s="3">
         <v>4100</v>
       </c>
       <c r="AB22" s="3">
+        <v>4100</v>
+      </c>
+      <c r="AC22" s="3">
         <v>2400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2600</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>2700</v>
       </c>
       <c r="AE22" s="3">
         <v>2700</v>
@@ -1991,192 +2031,201 @@
       <c r="AF22" s="3">
         <v>2700</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-194600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-675800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-20400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>10000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-344700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>57900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>54800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>94500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-24100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>67000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>58000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>67500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-74500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-20200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>115800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>142100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>113700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>140900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>162900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>116900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>109300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-51200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>51500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>18200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>47400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>31600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-32200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-100300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-8300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-3200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-57600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>12000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>8600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>10700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-7400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>12200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>15800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-14100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>14400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>11700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>9500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-162400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-575500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>13200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-287200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>53100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>48000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>82500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-23400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>59300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>49400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>56800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-13600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-67100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-21500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>103600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>126300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>127900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>126500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>151200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>107400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>108400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-52400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>50200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>17200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>46400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>31000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>15500</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-123500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-366100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-38400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-18500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-192000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>17600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>13300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>30800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-20200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>26200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>21300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>28800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-29200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-11000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>41800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>48300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>62100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>41700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>37800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>25600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-800</v>
       </c>
-      <c r="Z27" s="3">
-        <v>0</v>
-      </c>
       <c r="AA27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="3">
         <v>-84900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>12100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>44400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>28500</v>
       </c>
-      <c r="AE27" s="3">
-        <v>0</v>
-      </c>
       <c r="AF27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,49 +2886,52 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-31000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>200</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>4</v>
+      <c r="P32" s="3">
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>4</v>
@@ -2869,142 +2939,148 @@
       <c r="R32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S32" s="3">
-        <v>-23100</v>
+      <c r="S32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T32" s="3">
         <v>-23100</v>
       </c>
       <c r="U32" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="V32" s="3">
         <v>-3000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-3700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-7600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-123500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-366100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-38400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-18500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-192000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>17600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>13300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>30800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-20200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>26200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>21300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>28800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-29200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-11000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>41800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>48300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>62100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>41700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>37800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>25600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-800</v>
       </c>
-      <c r="Z33" s="3">
-        <v>0</v>
-      </c>
       <c r="AA33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="3">
         <v>-84900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>12100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>44400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>28500</v>
       </c>
-      <c r="AE33" s="3">
-        <v>0</v>
-      </c>
       <c r="AF33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-123500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-366100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-38400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-18500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-192000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>17600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>13300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>30800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-20200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>26200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>21300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>28800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-29200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-11000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>41800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>48300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>62100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>41700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>37800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>25600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-800</v>
       </c>
-      <c r="Z35" s="3">
-        <v>0</v>
-      </c>
       <c r="AA35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="3">
         <v>-84900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>12100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>44400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>28500</v>
       </c>
-      <c r="AE35" s="3">
-        <v>0</v>
-      </c>
       <c r="AF35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,89 +3438,90 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1118400</v>
+      </c>
+      <c r="E41" s="3">
         <v>377500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>366200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>244100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>289300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>278800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>224600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>195400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>181600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>173600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>176100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>127200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>128600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>140100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>143600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>106400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>116400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>135900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>175000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>218600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>179900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>185000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>156900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>90700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>89900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>116100</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3444,8 +3531,11 @@
       <c r="AF41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,89 +3626,92 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2283300</v>
+      </c>
+      <c r="E43" s="3">
         <v>2250500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1933000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1780900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1669300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1634700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1529500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1487500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1478400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1326000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1428100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1386200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1325900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2093800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2228300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2583900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2868600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2702700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2469100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1121500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>936100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>669900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>518900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>369300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>495600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>426500</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3628,8 +3721,11 @@
       <c r="AF43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3669,8 +3765,8 @@
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3720,8 +3816,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3761,8 +3860,8 @@
       <c r="O45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
+      <c r="P45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q45" s="3">
         <v>0</v>
@@ -3812,50 +3911,53 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3402300</v>
+      </c>
+      <c r="E46" s="3">
         <v>2628500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2299700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2025600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1959100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1914200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1754900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1683600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1660700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1500300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1604900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1514200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1455500</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -3904,89 +4006,92 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1717600</v>
+      </c>
+      <c r="E47" s="3">
         <v>1068800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1537500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1359800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1227900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1065700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1012800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>921300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>898100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>869000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>898700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>906900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>916400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>123400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>107000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>108100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>107000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>98800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>90300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>82900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>74400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>63400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>57900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>50400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>53400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>49600</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>4</v>
       </c>
@@ -3996,71 +4101,74 @@
       <c r="AF47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>107900</v>
+      </c>
+      <c r="E48" s="3">
         <v>84000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>86600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>89100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>121600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>90600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>92800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>95400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>127300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>97400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>99800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>100500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>117000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>104800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>62800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>72100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>61100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>63300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>65500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>64700</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>4</v>
       </c>
@@ -4076,8 +4184,8 @@
       <c r="AB48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC48" s="3">
-        <v>0</v>
+      <c r="AC48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD48" s="3">
         <v>0</v>
@@ -4088,89 +4196,92 @@
       <c r="AF48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>803600</v>
+      </c>
+      <c r="E49" s="3">
         <v>813800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>824000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>834200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>844400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>854700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>864900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>875200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>885400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>895800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>913900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>924500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>935200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>946100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>956900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>967800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>978700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>992400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1003100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>11700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>12300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>13100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>14000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>14800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>15600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>16600</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD49" s="3" t="s">
         <v>4</v>
       </c>
@@ -4180,8 +4291,11 @@
       <c r="AF49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,89 +4481,92 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>116600</v>
+      </c>
+      <c r="E52" s="3">
         <v>62800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>60000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>70400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>50800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>68400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>69800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>63500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>32800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>60300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>54200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>45700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>29000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>50200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>40400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>32500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>28900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>20000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>98500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>93400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>39600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>47200</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA52" s="3">
+      <c r="AA52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB52" s="3">
         <v>700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>600</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>4</v>
       </c>
@@ -4456,8 +4576,11 @@
       <c r="AF52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,89 +4671,92 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6762700</v>
+      </c>
+      <c r="E54" s="3">
         <v>5241500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5332100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4782400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4586700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4349600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4039900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3834400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3788800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3468200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3608400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3530800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3497400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3503100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3575600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3906200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4188100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4036600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3831500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1622800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1320800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>994800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>817700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>549400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>680800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>631500</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>4</v>
       </c>
@@ -4640,8 +4766,11 @@
       <c r="AF54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,89 +4838,90 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>57300</v>
+      </c>
+      <c r="E57" s="3">
         <v>41100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>48500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>35800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>40200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>139100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>21400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>26000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>22300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>37000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>34000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>31000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>64700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>63600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>55400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>61500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>41500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>48900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>24800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>33800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>28400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>29300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>25400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>36000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>40900</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>4</v>
       </c>
@@ -4800,47 +4931,50 @@
       <c r="AF57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E58" s="3">
         <v>4300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>26200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>13000</v>
       </c>
-      <c r="G58" s="3">
-        <v>17000</v>
-      </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>4100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>8400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>12400</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>2700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>9100</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -4892,8 +5026,11 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4912,69 +5049,69 @@
       <c r="H59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3">
         <v>53700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1725400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1787000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2023600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2220400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2095800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1917900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>815600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>613400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>418700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>350400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>213000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>264500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>238900</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4984,50 +5121,53 @@
       <c r="AF59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4153800</v>
+      </c>
+      <c r="E60" s="3">
         <v>3946700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3337300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2323400</v>
       </c>
-      <c r="G60" s="3">
-        <v>2047600</v>
-      </c>
       <c r="H60" s="3">
+        <v>2030600</v>
+      </c>
+      <c r="I60" s="3">
         <v>2003600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1429100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1285500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1381100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1293800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1404800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1396100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1343000</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -5076,68 +5216,71 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1289400</v>
+      </c>
+      <c r="E61" s="3">
         <v>372400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>370700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>369000</v>
       </c>
-      <c r="G61" s="3">
-        <v>365800</v>
-      </c>
       <c r="H61" s="3">
+        <v>382800</v>
+      </c>
+      <c r="I61" s="3">
         <v>277000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>280100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>277800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>268600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>239500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>236700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>205500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>219600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>83200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>63100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>63000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>62900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>62800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>112600</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -5148,17 +5291,17 @@
         <v>0</v>
       </c>
       <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>143000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>143100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>143300</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
@@ -5168,50 +5311,53 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>388100</v>
+      </c>
+      <c r="E62" s="3">
         <v>356900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>353500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>344300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>349400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>325600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>274100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>281500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>214300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>244600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>244000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>234000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>241400</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
@@ -5236,21 +5382,21 @@
       <c r="X62" s="3">
         <v>0</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>4</v>
+      <c r="Y62" s="3">
+        <v>0</v>
       </c>
       <c r="Z62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AA62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB62" s="3">
         <v>200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>400</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>4</v>
       </c>
@@ -5260,8 +5406,11 @@
       <c r="AF62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,89 +5691,92 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5876700</v>
+      </c>
+      <c r="E66" s="3">
         <v>4722000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4106300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3085000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2812300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2606200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2039600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1894900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1915700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1802300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1910700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1860600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1844100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2751400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2814400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3106400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3370500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3260900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3147900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1317800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1071400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>848600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>698200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>414200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>464600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>444900</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>4</v>
       </c>
@@ -5628,8 +5786,11 @@
       <c r="AF66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,80 +6201,83 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-896900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-866300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-720400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-332000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-242500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-205700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>13800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>131300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>165200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>152600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>160400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>144500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>164000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>205900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>229600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>197200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>158100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>99100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>60400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>24800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-800</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>4</v>
       </c>
@@ -6122,8 +6296,11 @@
       <c r="AF72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,89 +6581,92 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-413600</v>
+      </c>
+      <c r="E76" s="3">
         <v>-378800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-233500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>153900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>179400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>209800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>397500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>366900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>324500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>761800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>794700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>766000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>771600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>751700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>761200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>799800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>817600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>775700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>683600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>304900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>249400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>146200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>119600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>135200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>216200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>186600</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>4</v>
       </c>
@@ -6490,8 +6676,11 @@
       <c r="AF76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-123500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-366100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-38400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-18500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-192000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>17600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>13300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>30800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-20200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>26200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>21300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>28800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-29200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-11000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>41800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>48300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>62100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>41700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>37800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>25600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-800</v>
       </c>
-      <c r="Z81" s="3">
-        <v>0</v>
-      </c>
       <c r="AA81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB81" s="3">
         <v>-84900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>12100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>44400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>28500</v>
       </c>
-      <c r="AE81" s="3">
-        <v>0</v>
-      </c>
       <c r="AF81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,73 +7003,74 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E83" s="3">
         <v>1100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1200</v>
-      </c>
-      <c r="F83" s="3">
-        <v>1000</v>
       </c>
       <c r="G83" s="3">
         <v>1000</v>
       </c>
       <c r="H83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I83" s="3">
         <v>900</v>
-      </c>
-      <c r="I83" s="3">
-        <v>700</v>
       </c>
       <c r="J83" s="3">
         <v>700</v>
       </c>
       <c r="K83" s="3">
+        <v>700</v>
+      </c>
+      <c r="L83" s="3">
         <v>500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>700</v>
-      </c>
-      <c r="N83" s="3">
-        <v>600</v>
       </c>
       <c r="O83" s="3">
         <v>600</v>
       </c>
       <c r="P83" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q83" s="3">
         <v>12100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>11700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>11500</v>
-      </c>
-      <c r="S83" s="3">
-        <v>11700</v>
       </c>
       <c r="T83" s="3">
         <v>11700</v>
       </c>
       <c r="U83" s="3">
+        <v>11700</v>
+      </c>
+      <c r="V83" s="3">
         <v>2400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1300</v>
-      </c>
-      <c r="X83" s="3">
-        <v>1400</v>
       </c>
       <c r="Y83" s="3">
         <v>1400</v>
@@ -6880,25 +7079,28 @@
         <v>1400</v>
       </c>
       <c r="AA83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AB83" s="3">
         <v>1600</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AD83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE83" s="3">
         <v>1700</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7571,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="E89" s="3">
         <v>27200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>16200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>46300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-66500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>27600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>53700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>50200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>25200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>71100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>57600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>88200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>57500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>32300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>46500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>59800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>75700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>29000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>37400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>53900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>28900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AD89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE89" s="3">
         <v>26400</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7703,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1200</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-300</v>
       </c>
       <c r="X91" s="3">
         <v>-300</v>
       </c>
       <c r="Y91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-700</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AD91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-100</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7986,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>821700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-67300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-9800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-11800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-20900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-10900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-12900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-14500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-7400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-9700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-8800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-11500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-184300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AD94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE94" s="3">
         <v>1300</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,68 +8118,69 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E96" s="3">
         <v>22100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>22000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>18900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>18000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>17200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>16200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>13900</v>
-      </c>
-      <c r="K96" s="3">
-        <v>13400</v>
       </c>
       <c r="L96" s="3">
         <v>13400</v>
       </c>
       <c r="M96" s="3">
+        <v>13400</v>
+      </c>
+      <c r="N96" s="3">
         <v>13200</v>
-      </c>
-      <c r="N96" s="3">
-        <v>12600</v>
       </c>
       <c r="O96" s="3">
         <v>12600</v>
       </c>
       <c r="P96" s="3">
+        <v>12600</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-12900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-12300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-12200</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-9100</v>
       </c>
       <c r="T96" s="3">
         <v>-9100</v>
       </c>
       <c r="U96" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="V96" s="3">
         <v>-5600</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8496,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-57800</v>
+      </c>
+      <c r="E100" s="3">
         <v>51800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>115600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-72200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>84900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>26200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-22900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>9300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-13800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-9500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-44000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-42100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-60700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-43400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-74200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>77600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-30500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-32800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>19400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-26600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-21800</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AD100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-10500</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E101" s="3">
         <v>2900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1300</v>
-      </c>
-      <c r="X101" s="3">
-        <v>-100</v>
       </c>
       <c r="Y101" s="3">
         <v>-100</v>
       </c>
       <c r="Z101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA101" s="3">
         <v>100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-200</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE101" s="3" t="s">
-        <v>4</v>
+      <c r="AD101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>0</v>
       </c>
       <c r="AF101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>741000</v>
+      </c>
+      <c r="E102" s="3">
         <v>11300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>122100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-45100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>10300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>54100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>29200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>13900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>8000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>48900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-11500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>37200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-10100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-19500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-39100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-46600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>38700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-5100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>29200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>69100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-26200</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AD102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE102" s="3">
         <v>17200</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
